--- a/Книги.xlsx
+++ b/Книги.xlsx
@@ -1,19 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11211"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dmitrypotekhin/Downloads/dmpotekhin.github.io/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58AC6FE8-5FCE-3B4B-9F86-097CC3819155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="16000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Книги" sheetId="1" r:id="rId5"/>
+    <sheet name="Книги" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Книги'!$A$1:$C$508</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Книги!$A$1:$C$508</definedName>
   </definedNames>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1562" uniqueCount="848">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1574" uniqueCount="856">
   <si>
     <t>Борис Акунин</t>
   </si>
@@ -2558,31 +2568,65 @@
   </si>
   <si>
     <t>Исскуство мыслить успешно</t>
+  </si>
+  <si>
+    <t>Нгуен Тхи Нинь</t>
+  </si>
+  <si>
+    <t>Вьетнам полная история страны</t>
+  </si>
+  <si>
+    <t>Алекс Хормози</t>
+  </si>
+  <si>
+    <t>100 млн офферы</t>
+  </si>
+  <si>
+    <t>Анна Марчук</t>
+  </si>
+  <si>
+    <t>Хитрый, как лис,ловкий, как тигр 36 китайских стратагем</t>
+  </si>
+  <si>
+    <t>Рей Далио</t>
+  </si>
+  <si>
+    <t>Принципы Жизнь и работа</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2591,11 +2635,17 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="2">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -2609,37 +2659,34 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2647,7 +2694,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -2837,26 +2884,29 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:U526"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="21.0"/>
-    <col customWidth="1" min="2" max="2" width="45.13"/>
-    <col customWidth="1" min="3" max="3" width="32.13"/>
+    <col min="1" max="1" width="21" customWidth="1"/>
+    <col min="2" max="2" width="45.1640625" customWidth="1"/>
+    <col min="3" max="3" width="32.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2867,7 +2917,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -2878,7 +2928,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -2889,7 +2939,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -2900,7 +2950,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
@@ -2911,7 +2961,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
@@ -2922,7 +2972,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
         <v>0</v>
       </c>
@@ -2933,7 +2983,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
         <v>0</v>
       </c>
@@ -2944,7 +2994,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -2955,7 +3005,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A11" s="1" t="s">
         <v>0</v>
       </c>
@@ -2984,7 +3034,7 @@
       <c r="T11" s="2"/>
       <c r="U11" s="2"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
         <v>0</v>
       </c>
@@ -3013,7 +3063,7 @@
       <c r="T12" s="2"/>
       <c r="U12" s="2"/>
     </row>
-    <row r="13">
+    <row r="13" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
         <v>0</v>
       </c>
@@ -3042,7 +3092,7 @@
       <c r="T13" s="2"/>
       <c r="U13" s="2"/>
     </row>
-    <row r="14">
+    <row r="14" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
         <v>0</v>
       </c>
@@ -3071,7 +3121,7 @@
       <c r="T14" s="2"/>
       <c r="U14" s="2"/>
     </row>
-    <row r="15">
+    <row r="15" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
         <v>0</v>
       </c>
@@ -3100,7 +3150,7 @@
       <c r="T15" s="2"/>
       <c r="U15" s="2"/>
     </row>
-    <row r="16">
+    <row r="16" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A16" s="1" t="s">
         <v>0</v>
       </c>
@@ -3129,7 +3179,7 @@
       <c r="T16" s="2"/>
       <c r="U16" s="2"/>
     </row>
-    <row r="17">
+    <row r="17" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
         <v>0</v>
       </c>
@@ -3158,7 +3208,7 @@
       <c r="T17" s="2"/>
       <c r="U17" s="2"/>
     </row>
-    <row r="18">
+    <row r="18" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A18" s="1" t="s">
         <v>0</v>
       </c>
@@ -3187,7 +3237,7 @@
       <c r="T18" s="2"/>
       <c r="U18" s="2"/>
     </row>
-    <row r="19">
+    <row r="19" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
         <v>0</v>
       </c>
@@ -3216,7 +3266,7 @@
       <c r="T19" s="2"/>
       <c r="U19" s="2"/>
     </row>
-    <row r="20">
+    <row r="20" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A20" s="1" t="s">
         <v>20</v>
       </c>
@@ -3245,7 +3295,7 @@
       <c r="T20" s="2"/>
       <c r="U20" s="2"/>
     </row>
-    <row r="21">
+    <row r="21" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
@@ -3274,7 +3324,7 @@
       <c r="T21" s="2"/>
       <c r="U21" s="2"/>
     </row>
-    <row r="22">
+    <row r="22" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
         <v>23</v>
       </c>
@@ -3303,7 +3353,7 @@
       <c r="T22" s="2"/>
       <c r="U22" s="2"/>
     </row>
-    <row r="23">
+    <row r="23" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
         <v>25</v>
       </c>
@@ -3332,7 +3382,7 @@
       <c r="T23" s="2"/>
       <c r="U23" s="2"/>
     </row>
-    <row r="24">
+    <row r="24" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A24" s="1" t="s">
         <v>25</v>
       </c>
@@ -3361,7 +3411,7 @@
       <c r="T24" s="2"/>
       <c r="U24" s="2"/>
     </row>
-    <row r="25">
+    <row r="25" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A25" s="1" t="s">
         <v>28</v>
       </c>
@@ -3390,7 +3440,7 @@
       <c r="T25" s="2"/>
       <c r="U25" s="2"/>
     </row>
-    <row r="26">
+    <row r="26" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A26" s="1" t="s">
         <v>30</v>
       </c>
@@ -3419,7 +3469,7 @@
       <c r="T26" s="2"/>
       <c r="U26" s="2"/>
     </row>
-    <row r="27">
+    <row r="27" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A27" s="1" t="s">
         <v>32</v>
       </c>
@@ -3448,7 +3498,7 @@
       <c r="T27" s="2"/>
       <c r="U27" s="2"/>
     </row>
-    <row r="28">
+    <row r="28" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A28" s="1" t="s">
         <v>32</v>
       </c>
@@ -3477,7 +3527,7 @@
       <c r="T28" s="2"/>
       <c r="U28" s="2"/>
     </row>
-    <row r="29">
+    <row r="29" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A29" s="1" t="s">
         <v>35</v>
       </c>
@@ -3506,7 +3556,7 @@
       <c r="T29" s="2"/>
       <c r="U29" s="2"/>
     </row>
-    <row r="30">
+    <row r="30" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A30" s="1" t="s">
         <v>35</v>
       </c>
@@ -3535,7 +3585,7 @@
       <c r="T30" s="2"/>
       <c r="U30" s="2"/>
     </row>
-    <row r="31">
+    <row r="31" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A31" s="1" t="s">
         <v>35</v>
       </c>
@@ -3564,7 +3614,7 @@
       <c r="T31" s="2"/>
       <c r="U31" s="2"/>
     </row>
-    <row r="32">
+    <row r="32" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A32" s="1" t="s">
         <v>39</v>
       </c>
@@ -3593,7 +3643,7 @@
       <c r="T32" s="2"/>
       <c r="U32" s="2"/>
     </row>
-    <row r="33">
+    <row r="33" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A33" s="1" t="s">
         <v>41</v>
       </c>
@@ -3622,7 +3672,7 @@
       <c r="T33" s="2"/>
       <c r="U33" s="2"/>
     </row>
-    <row r="34">
+    <row r="34" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
         <v>43</v>
       </c>
@@ -3651,7 +3701,7 @@
       <c r="T34" s="2"/>
       <c r="U34" s="2"/>
     </row>
-    <row r="35">
+    <row r="35" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
         <v>45</v>
       </c>
@@ -3680,7 +3730,7 @@
       <c r="T35" s="2"/>
       <c r="U35" s="2"/>
     </row>
-    <row r="36">
+    <row r="36" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
         <v>47</v>
       </c>
@@ -3709,7 +3759,7 @@
       <c r="T36" s="2"/>
       <c r="U36" s="2"/>
     </row>
-    <row r="37">
+    <row r="37" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A37" s="1" t="s">
         <v>47</v>
       </c>
@@ -3738,7 +3788,7 @@
       <c r="T37" s="2"/>
       <c r="U37" s="2"/>
     </row>
-    <row r="38">
+    <row r="38" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A38" s="1" t="s">
         <v>47</v>
       </c>
@@ -3767,7 +3817,7 @@
       <c r="T38" s="2"/>
       <c r="U38" s="2"/>
     </row>
-    <row r="39">
+    <row r="39" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A39" s="1" t="s">
         <v>51</v>
       </c>
@@ -3796,7 +3846,7 @@
       <c r="T39" s="2"/>
       <c r="U39" s="2"/>
     </row>
-    <row r="40">
+    <row r="40" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A40" s="1" t="s">
         <v>53</v>
       </c>
@@ -3825,7 +3875,7 @@
       <c r="T40" s="2"/>
       <c r="U40" s="2"/>
     </row>
-    <row r="41">
+    <row r="41" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A41" s="1" t="s">
         <v>55</v>
       </c>
@@ -3854,7 +3904,7 @@
       <c r="T41" s="2"/>
       <c r="U41" s="2"/>
     </row>
-    <row r="42">
+    <row r="42" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A42" s="1" t="s">
         <v>55</v>
       </c>
@@ -3883,7 +3933,7 @@
       <c r="T42" s="2"/>
       <c r="U42" s="2"/>
     </row>
-    <row r="43">
+    <row r="43" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A43" s="1" t="s">
         <v>58</v>
       </c>
@@ -3912,7 +3962,7 @@
       <c r="T43" s="2"/>
       <c r="U43" s="2"/>
     </row>
-    <row r="44">
+    <row r="44" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A44" s="1" t="s">
         <v>60</v>
       </c>
@@ -3941,7 +3991,7 @@
       <c r="T44" s="2"/>
       <c r="U44" s="2"/>
     </row>
-    <row r="45">
+    <row r="45" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A45" s="1" t="s">
         <v>62</v>
       </c>
@@ -3970,7 +4020,7 @@
       <c r="T45" s="2"/>
       <c r="U45" s="2"/>
     </row>
-    <row r="46">
+    <row r="46" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A46" s="1" t="s">
         <v>64</v>
       </c>
@@ -3999,7 +4049,7 @@
       <c r="T46" s="2"/>
       <c r="U46" s="2"/>
     </row>
-    <row r="47">
+    <row r="47" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
         <v>66</v>
       </c>
@@ -4028,7 +4078,7 @@
       <c r="T47" s="2"/>
       <c r="U47" s="2"/>
     </row>
-    <row r="48">
+    <row r="48" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A48" s="1" t="s">
         <v>68</v>
       </c>
@@ -4057,7 +4107,7 @@
       <c r="T48" s="2"/>
       <c r="U48" s="2"/>
     </row>
-    <row r="49">
+    <row r="49" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A49" s="1" t="s">
         <v>71</v>
       </c>
@@ -4086,7 +4136,7 @@
       <c r="T49" s="2"/>
       <c r="U49" s="2"/>
     </row>
-    <row r="50">
+    <row r="50" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A50" s="1" t="s">
         <v>73</v>
       </c>
@@ -4115,7 +4165,7 @@
       <c r="T50" s="2"/>
       <c r="U50" s="2"/>
     </row>
-    <row r="51">
+    <row r="51" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A51" s="1" t="s">
         <v>51</v>
       </c>
@@ -4144,7 +4194,7 @@
       <c r="T51" s="2"/>
       <c r="U51" s="2"/>
     </row>
-    <row r="52">
+    <row r="52" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A52" s="1" t="s">
         <v>51</v>
       </c>
@@ -4173,7 +4223,7 @@
       <c r="T52" s="2"/>
       <c r="U52" s="2"/>
     </row>
-    <row r="53">
+    <row r="53" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A53" s="1" t="s">
         <v>51</v>
       </c>
@@ -4202,7 +4252,7 @@
       <c r="T53" s="2"/>
       <c r="U53" s="2"/>
     </row>
-    <row r="54">
+    <row r="54" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A54" s="1" t="s">
         <v>78</v>
       </c>
@@ -4231,7 +4281,7 @@
       <c r="T54" s="2"/>
       <c r="U54" s="2"/>
     </row>
-    <row r="55">
+    <row r="55" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A55" s="1" t="s">
         <v>78</v>
       </c>
@@ -4260,7 +4310,7 @@
       <c r="T55" s="2"/>
       <c r="U55" s="2"/>
     </row>
-    <row r="56">
+    <row r="56" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A56" s="1" t="s">
         <v>78</v>
       </c>
@@ -4271,7 +4321,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A57" s="1" t="s">
         <v>78</v>
       </c>
@@ -4282,7 +4332,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A58" s="1" t="s">
         <v>78</v>
       </c>
@@ -4293,7 +4343,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A59" s="1" t="s">
         <v>78</v>
       </c>
@@ -4304,7 +4354,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A60" s="1" t="s">
         <v>78</v>
       </c>
@@ -4315,7 +4365,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A61" s="1" t="s">
         <v>78</v>
       </c>
@@ -4326,7 +4376,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A62" s="1" t="s">
         <v>78</v>
       </c>
@@ -4337,7 +4387,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A63" s="1" t="s">
         <v>78</v>
       </c>
@@ -4348,7 +4398,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:21" ht="13" x14ac:dyDescent="0.15">
       <c r="A64" s="1" t="s">
         <v>78</v>
       </c>
@@ -4359,7 +4409,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A65" s="1" t="s">
         <v>78</v>
       </c>
@@ -4370,7 +4420,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A66" s="1" t="s">
         <v>78</v>
       </c>
@@ -4381,7 +4431,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A67" s="1" t="s">
         <v>78</v>
       </c>
@@ -4392,7 +4442,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A68" s="1" t="s">
         <v>78</v>
       </c>
@@ -4403,7 +4453,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A69" s="1" t="s">
         <v>94</v>
       </c>
@@ -4414,7 +4464,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A70" s="1" t="s">
         <v>94</v>
       </c>
@@ -4425,7 +4475,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A71" s="1" t="s">
         <v>35</v>
       </c>
@@ -4436,7 +4486,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A72" s="1" t="s">
         <v>98</v>
       </c>
@@ -4447,7 +4497,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A73" s="1" t="s">
         <v>100</v>
       </c>
@@ -4458,7 +4508,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A74" s="1" t="s">
         <v>102</v>
       </c>
@@ -4469,7 +4519,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A75" s="1" t="s">
         <v>104</v>
       </c>
@@ -4480,7 +4530,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A76" s="1" t="s">
         <v>106</v>
       </c>
@@ -4491,7 +4541,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A77" s="1" t="s">
         <v>106</v>
       </c>
@@ -4502,7 +4552,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A78" s="1" t="s">
         <v>106</v>
       </c>
@@ -4513,7 +4563,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A79" s="1" t="s">
         <v>111</v>
       </c>
@@ -4524,7 +4574,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A80" s="1" t="s">
         <v>113</v>
       </c>
@@ -4535,7 +4585,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A81" s="1" t="s">
         <v>113</v>
       </c>
@@ -4546,7 +4596,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A82" s="1" t="s">
         <v>113</v>
       </c>
@@ -4557,7 +4607,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A83" s="1" t="s">
         <v>117</v>
       </c>
@@ -4568,7 +4618,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A84" s="1" t="s">
         <v>119</v>
       </c>
@@ -4579,7 +4629,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A85" s="1" t="s">
         <v>121</v>
       </c>
@@ -4590,7 +4640,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A86" s="1" t="s">
         <v>123</v>
       </c>
@@ -4601,7 +4651,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A87" s="1" t="s">
         <v>125</v>
       </c>
@@ -4612,7 +4662,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A88" s="1" t="s">
         <v>127</v>
       </c>
@@ -4623,7 +4673,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A89" s="1" t="s">
         <v>129</v>
       </c>
@@ -4634,7 +4684,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A90" s="1" t="s">
         <v>131</v>
       </c>
@@ -4645,7 +4695,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A91" s="1" t="s">
         <v>133</v>
       </c>
@@ -4656,7 +4706,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A92" s="1" t="s">
         <v>131</v>
       </c>
@@ -4667,7 +4717,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A93" s="1" t="s">
         <v>136</v>
       </c>
@@ -4678,7 +4728,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A94" s="1" t="s">
         <v>138</v>
       </c>
@@ -4689,7 +4739,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A95" s="1" t="s">
         <v>140</v>
       </c>
@@ -4700,7 +4750,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A96" s="1" t="s">
         <v>142</v>
       </c>
@@ -4711,7 +4761,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A97" s="1" t="s">
         <v>144</v>
       </c>
@@ -4722,7 +4772,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A98" s="1" t="s">
         <v>146</v>
       </c>
@@ -4733,7 +4783,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A99" s="1" t="s">
         <v>148</v>
       </c>
@@ -4744,7 +4794,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A100" s="1" t="s">
         <v>150</v>
       </c>
@@ -4755,7 +4805,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A101" s="1" t="s">
         <v>152</v>
       </c>
@@ -4766,7 +4816,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A102" s="1" t="s">
         <v>154</v>
       </c>
@@ -4777,7 +4827,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A103" s="1" t="s">
         <v>156</v>
       </c>
@@ -4788,7 +4838,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A104" s="1" t="s">
         <v>156</v>
       </c>
@@ -4799,7 +4849,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A105" s="1" t="s">
         <v>156</v>
       </c>
@@ -4810,7 +4860,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A106" s="1" t="s">
         <v>160</v>
       </c>
@@ -4821,7 +4871,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A107" s="1" t="s">
         <v>160</v>
       </c>
@@ -4832,7 +4882,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A108" s="1" t="s">
         <v>163</v>
       </c>
@@ -4843,7 +4893,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A109" s="1" t="s">
         <v>163</v>
       </c>
@@ -4854,7 +4904,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A110" s="1" t="s">
         <v>163</v>
       </c>
@@ -4865,7 +4915,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A111" s="1" t="s">
         <v>167</v>
       </c>
@@ -4876,7 +4926,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A112" s="1" t="s">
         <v>170</v>
       </c>
@@ -4887,7 +4937,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A113" s="1" t="s">
         <v>172</v>
       </c>
@@ -4898,7 +4948,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A114" s="1" t="s">
         <v>174</v>
       </c>
@@ -4909,7 +4959,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A115" s="1" t="s">
         <v>176</v>
       </c>
@@ -4920,7 +4970,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A116" s="1" t="s">
         <v>176</v>
       </c>
@@ -4931,7 +4981,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A117" s="1" t="s">
         <v>154</v>
       </c>
@@ -4942,7 +4992,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A118" s="1" t="s">
         <v>154</v>
       </c>
@@ -4953,7 +5003,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A119" s="1" t="s">
         <v>154</v>
       </c>
@@ -4964,7 +5014,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A120" s="1" t="s">
         <v>182</v>
       </c>
@@ -4975,7 +5025,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A121" s="1" t="s">
         <v>182</v>
       </c>
@@ -4986,7 +5036,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A122" s="1" t="s">
         <v>185</v>
       </c>
@@ -4997,7 +5047,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A123" s="1" t="s">
         <v>187</v>
       </c>
@@ -5008,7 +5058,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A124" s="1" t="s">
         <v>187</v>
       </c>
@@ -5019,7 +5069,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A125" s="1" t="s">
         <v>187</v>
       </c>
@@ -5030,7 +5080,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A126" s="1" t="s">
         <v>191</v>
       </c>
@@ -5041,7 +5091,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A127" s="1" t="s">
         <v>191</v>
       </c>
@@ -5052,7 +5102,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A128" s="1" t="s">
         <v>194</v>
       </c>
@@ -5063,7 +5113,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A129" s="1" t="s">
         <v>194</v>
       </c>
@@ -5074,7 +5124,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A130" s="1" t="s">
         <v>197</v>
       </c>
@@ -5085,7 +5135,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A131" s="1" t="s">
         <v>199</v>
       </c>
@@ -5096,7 +5146,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A132" s="1" t="s">
         <v>197</v>
       </c>
@@ -5107,7 +5157,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A133" s="1" t="s">
         <v>202</v>
       </c>
@@ -5118,7 +5168,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A134" s="1" t="s">
         <v>204</v>
       </c>
@@ -5129,7 +5179,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A135" s="1" t="s">
         <v>206</v>
       </c>
@@ -5140,7 +5190,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A136" s="1" t="s">
         <v>208</v>
       </c>
@@ -5151,7 +5201,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A137" s="1" t="s">
         <v>210</v>
       </c>
@@ -5162,7 +5212,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A138" s="1" t="s">
         <v>210</v>
       </c>
@@ -5173,7 +5223,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A139" s="1" t="s">
         <v>213</v>
       </c>
@@ -5184,7 +5234,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A140" s="1" t="s">
         <v>215</v>
       </c>
@@ -5195,7 +5245,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A141" s="1" t="s">
         <v>217</v>
       </c>
@@ -5206,7 +5256,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A142" s="1" t="s">
         <v>219</v>
       </c>
@@ -5217,7 +5267,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A143" s="1" t="s">
         <v>221</v>
       </c>
@@ -5228,7 +5278,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A144" s="1" t="s">
         <v>223</v>
       </c>
@@ -5239,7 +5289,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="145">
+    <row r="145" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A145" s="1" t="s">
         <v>225</v>
       </c>
@@ -5250,7 +5300,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A146" s="1" t="s">
         <v>227</v>
       </c>
@@ -5261,7 +5311,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A147" s="1" t="s">
         <v>227</v>
       </c>
@@ -5272,7 +5322,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A148" s="1" t="s">
         <v>172</v>
       </c>
@@ -5283,7 +5333,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A149" s="1" t="s">
         <v>231</v>
       </c>
@@ -5294,7 +5344,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A150" s="1" t="s">
         <v>231</v>
       </c>
@@ -5305,7 +5355,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A151" s="1" t="s">
         <v>234</v>
       </c>
@@ -5316,7 +5366,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A152" s="1" t="s">
         <v>236</v>
       </c>
@@ -5327,7 +5377,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A153" s="1" t="s">
         <v>238</v>
       </c>
@@ -5338,7 +5388,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A154" s="1" t="s">
         <v>240</v>
       </c>
@@ -5349,7 +5399,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A155" s="1" t="s">
         <v>242</v>
       </c>
@@ -5360,7 +5410,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A156" s="1" t="s">
         <v>244</v>
       </c>
@@ -5371,7 +5421,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="157">
+    <row r="157" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A157" s="1" t="s">
         <v>244</v>
       </c>
@@ -5382,7 +5432,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="158">
+    <row r="158" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A158" s="1" t="s">
         <v>244</v>
       </c>
@@ -5393,7 +5443,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A159" s="1" t="s">
         <v>244</v>
       </c>
@@ -5404,7 +5454,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="160">
+    <row r="160" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A160" s="1" t="s">
         <v>249</v>
       </c>
@@ -5415,7 +5465,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="161">
+    <row r="161" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A161" s="1" t="s">
         <v>251</v>
       </c>
@@ -5426,7 +5476,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A162" s="1" t="s">
         <v>253</v>
       </c>
@@ -5437,7 +5487,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="163">
+    <row r="163" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A163" s="1" t="s">
         <v>255</v>
       </c>
@@ -5448,7 +5498,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A164" s="1" t="s">
         <v>255</v>
       </c>
@@ -5459,7 +5509,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="165">
+    <row r="165" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A165" s="1" t="s">
         <v>255</v>
       </c>
@@ -5470,7 +5520,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="166">
+    <row r="166" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A166" s="1" t="s">
         <v>259</v>
       </c>
@@ -5481,7 +5531,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="167">
+    <row r="167" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A167" s="1" t="s">
         <v>259</v>
       </c>
@@ -5492,7 +5542,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="168">
+    <row r="168" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A168" s="1" t="s">
         <v>262</v>
       </c>
@@ -5503,7 +5553,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A169" s="1" t="s">
         <v>262</v>
       </c>
@@ -5514,7 +5564,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A170" s="1" t="s">
         <v>262</v>
       </c>
@@ -5525,7 +5575,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="171">
+    <row r="171" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A171" s="1" t="s">
         <v>262</v>
       </c>
@@ -5536,7 +5586,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A172" s="1" t="s">
         <v>262</v>
       </c>
@@ -5547,7 +5597,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="173">
+    <row r="173" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A173" s="1" t="s">
         <v>268</v>
       </c>
@@ -5558,7 +5608,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="174">
+    <row r="174" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A174" s="1" t="s">
         <v>270</v>
       </c>
@@ -5569,7 +5619,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="175">
+    <row r="175" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A175" s="1" t="s">
         <v>272</v>
       </c>
@@ -5580,7 +5630,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="176">
+    <row r="176" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A176" s="1" t="s">
         <v>274</v>
       </c>
@@ -5591,7 +5641,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="177">
+    <row r="177" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A177" s="1" t="s">
         <v>276</v>
       </c>
@@ -5602,7 +5652,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="178">
+    <row r="178" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A178" s="1" t="s">
         <v>272</v>
       </c>
@@ -5613,7 +5663,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="179">
+    <row r="179" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A179" s="1" t="s">
         <v>279</v>
       </c>
@@ -5624,7 +5674,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="180">
+    <row r="180" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A180" s="1" t="s">
         <v>281</v>
       </c>
@@ -5635,7 +5685,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="181">
+    <row r="181" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A181" s="1" t="s">
         <v>53</v>
       </c>
@@ -5646,7 +5696,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="182">
+    <row r="182" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A182" s="1" t="s">
         <v>284</v>
       </c>
@@ -5657,7 +5707,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="183">
+    <row r="183" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A183" s="1" t="s">
         <v>286</v>
       </c>
@@ -5668,7 +5718,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="184">
+    <row r="184" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A184" s="1" t="s">
         <v>288</v>
       </c>
@@ -5679,7 +5729,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="185">
+    <row r="185" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A185" s="1" t="s">
         <v>288</v>
       </c>
@@ -5690,7 +5740,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="186">
+    <row r="186" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A186" s="1" t="s">
         <v>291</v>
       </c>
@@ -5701,7 +5751,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="187">
+    <row r="187" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A187" s="1" t="s">
         <v>293</v>
       </c>
@@ -5712,7 +5762,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="188">
+    <row r="188" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A188" s="1" t="s">
         <v>295</v>
       </c>
@@ -5723,7 +5773,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="189">
+    <row r="189" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A189" s="1" t="s">
         <v>297</v>
       </c>
@@ -5734,7 +5784,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="190">
+    <row r="190" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A190" s="1" t="s">
         <v>299</v>
       </c>
@@ -5745,7 +5795,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="191">
+    <row r="191" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A191" s="1" t="s">
         <v>47</v>
       </c>
@@ -5756,7 +5806,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="192">
+    <row r="192" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A192" s="1" t="s">
         <v>301</v>
       </c>
@@ -5767,7 +5817,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="193">
+    <row r="193" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A193" s="1" t="s">
         <v>303</v>
       </c>
@@ -5778,7 +5828,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="194">
+    <row r="194" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A194" s="1" t="s">
         <v>305</v>
       </c>
@@ -5789,7 +5839,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="195">
+    <row r="195" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A195" s="1" t="s">
         <v>305</v>
       </c>
@@ -5800,7 +5850,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="196">
+    <row r="196" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A196" s="1" t="s">
         <v>308</v>
       </c>
@@ -5811,7 +5861,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="197">
+    <row r="197" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A197" s="1" t="s">
         <v>310</v>
       </c>
@@ -5822,7 +5872,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="198">
+    <row r="198" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A198" s="1" t="s">
         <v>312</v>
       </c>
@@ -5833,7 +5883,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="199">
+    <row r="199" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A199" s="1" t="s">
         <v>314</v>
       </c>
@@ -5844,7 +5894,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="200">
+    <row r="200" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A200" s="1" t="s">
         <v>316</v>
       </c>
@@ -5855,7 +5905,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="201">
+    <row r="201" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A201" s="1" t="s">
         <v>318</v>
       </c>
@@ -5866,7 +5916,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="202">
+    <row r="202" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A202" s="1" t="s">
         <v>320</v>
       </c>
@@ -5877,7 +5927,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="203">
+    <row r="203" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A203" s="1" t="s">
         <v>316</v>
       </c>
@@ -5888,7 +5938,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="204">
+    <row r="204" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A204" s="1" t="s">
         <v>323</v>
       </c>
@@ -5899,7 +5949,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="205">
+    <row r="205" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A205" s="1" t="s">
         <v>325</v>
       </c>
@@ -5910,7 +5960,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="206">
+    <row r="206" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A206" s="1" t="s">
         <v>327</v>
       </c>
@@ -5921,7 +5971,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="207">
+    <row r="207" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A207" s="1" t="s">
         <v>329</v>
       </c>
@@ -5932,7 +5982,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="208">
+    <row r="208" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A208" s="1" t="s">
         <v>331</v>
       </c>
@@ -5943,7 +5993,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="209">
+    <row r="209" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A209" s="1" t="s">
         <v>333</v>
       </c>
@@ -5954,7 +6004,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="210">
+    <row r="210" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A210" s="1" t="s">
         <v>333</v>
       </c>
@@ -5965,7 +6015,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="211">
+    <row r="211" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A211" s="1" t="s">
         <v>336</v>
       </c>
@@ -5976,7 +6026,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="212">
+    <row r="212" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A212" s="1" t="s">
         <v>338</v>
       </c>
@@ -5987,7 +6037,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="213">
+    <row r="213" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A213" s="1" t="s">
         <v>340</v>
       </c>
@@ -5998,7 +6048,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="214">
+    <row r="214" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A214" s="1" t="s">
         <v>342</v>
       </c>
@@ -6009,7 +6059,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="215">
+    <row r="215" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A215" s="1" t="s">
         <v>344</v>
       </c>
@@ -6020,7 +6070,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="216">
+    <row r="216" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A216" s="1" t="s">
         <v>346</v>
       </c>
@@ -6031,7 +6081,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="217">
+    <row r="217" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A217" s="1" t="s">
         <v>348</v>
       </c>
@@ -6042,7 +6092,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="218">
+    <row r="218" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A218" s="1" t="s">
         <v>350</v>
       </c>
@@ -6053,7 +6103,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="219">
+    <row r="219" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A219" s="1" t="s">
         <v>352</v>
       </c>
@@ -6064,7 +6114,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="220">
+    <row r="220" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A220" s="1" t="s">
         <v>354</v>
       </c>
@@ -6075,7 +6125,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="221">
+    <row r="221" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A221" s="1" t="s">
         <v>356</v>
       </c>
@@ -6086,7 +6136,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="222">
+    <row r="222" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A222" s="1" t="s">
         <v>358</v>
       </c>
@@ -6097,7 +6147,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="223">
+    <row r="223" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A223" s="1" t="s">
         <v>360</v>
       </c>
@@ -6108,7 +6158,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="224">
+    <row r="224" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A224" s="1" t="s">
         <v>362</v>
       </c>
@@ -6119,7 +6169,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="225">
+    <row r="225" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A225" s="1" t="s">
         <v>364</v>
       </c>
@@ -6130,7 +6180,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="226">
+    <row r="226" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A226" s="1" t="s">
         <v>366</v>
       </c>
@@ -6141,7 +6191,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="227">
+    <row r="227" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A227" s="1" t="s">
         <v>262</v>
       </c>
@@ -6152,7 +6202,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="228">
+    <row r="228" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A228" s="1" t="s">
         <v>369</v>
       </c>
@@ -6163,7 +6213,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="229">
+    <row r="229" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A229" s="1" t="s">
         <v>371</v>
       </c>
@@ -6174,7 +6224,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="230">
+    <row r="230" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A230" s="1" t="s">
         <v>373</v>
       </c>
@@ -6185,7 +6235,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="231">
+    <row r="231" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A231" s="1" t="s">
         <v>375</v>
       </c>
@@ -6196,7 +6246,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="232">
+    <row r="232" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A232" s="1" t="s">
         <v>377</v>
       </c>
@@ -6207,7 +6257,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="233">
+    <row r="233" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A233" s="1" t="s">
         <v>379</v>
       </c>
@@ -6218,7 +6268,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="234">
+    <row r="234" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A234" s="1" t="s">
         <v>381</v>
       </c>
@@ -6229,7 +6279,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="235">
+    <row r="235" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A235" s="3" t="s">
         <v>129</v>
       </c>
@@ -6240,7 +6290,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="236">
+    <row r="236" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A236" s="3" t="s">
         <v>129</v>
       </c>
@@ -6251,7 +6301,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="237">
+    <row r="237" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A237" s="3" t="s">
         <v>385</v>
       </c>
@@ -6262,7 +6312,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="238">
+    <row r="238" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A238" s="3" t="s">
         <v>387</v>
       </c>
@@ -6273,7 +6323,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="239">
+    <row r="239" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A239" s="3" t="s">
         <v>389</v>
       </c>
@@ -6284,7 +6334,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="240">
+    <row r="240" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A240" s="3" t="s">
         <v>391</v>
       </c>
@@ -6295,7 +6345,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="241">
+    <row r="241" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A241" s="3" t="s">
         <v>350</v>
       </c>
@@ -6306,7 +6356,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="242">
+    <row r="242" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A242" s="3" t="s">
         <v>394</v>
       </c>
@@ -6317,7 +6367,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="243">
+    <row r="243" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A243" s="3" t="s">
         <v>396</v>
       </c>
@@ -6328,7 +6378,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="244">
+    <row r="244" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A244" s="3" t="s">
         <v>398</v>
       </c>
@@ -6339,7 +6389,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="245">
+    <row r="245" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A245" s="3" t="s">
         <v>400</v>
       </c>
@@ -6350,7 +6400,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="246">
+    <row r="246" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A246" s="3" t="s">
         <v>402</v>
       </c>
@@ -6361,7 +6411,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="247">
+    <row r="247" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A247" s="1" t="s">
         <v>404</v>
       </c>
@@ -6372,7 +6422,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="248">
+    <row r="248" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A248" s="1" t="s">
         <v>406</v>
       </c>
@@ -6383,7 +6433,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="249">
+    <row r="249" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A249" s="1" t="s">
         <v>408</v>
       </c>
@@ -6394,7 +6444,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="250">
+    <row r="250" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A250" s="1" t="s">
         <v>410</v>
       </c>
@@ -6405,7 +6455,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="251">
+    <row r="251" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A251" s="1" t="s">
         <v>412</v>
       </c>
@@ -6416,7 +6466,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="252">
+    <row r="252" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A252" s="1" t="s">
         <v>414</v>
       </c>
@@ -6427,7 +6477,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="253">
+    <row r="253" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A253" s="1" t="s">
         <v>416</v>
       </c>
@@ -6438,7 +6488,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="254">
+    <row r="254" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A254" s="1" t="s">
         <v>418</v>
       </c>
@@ -6449,7 +6499,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="255">
+    <row r="255" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A255" s="1" t="s">
         <v>420</v>
       </c>
@@ -6460,7 +6510,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="256">
+    <row r="256" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A256" s="1" t="s">
         <v>422</v>
       </c>
@@ -6471,7 +6521,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="257">
+    <row r="257" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A257" s="1" t="s">
         <v>424</v>
       </c>
@@ -6482,7 +6532,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="258" ht="17.25" customHeight="1">
+    <row r="258" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A258" s="1" t="s">
         <v>426</v>
       </c>
@@ -6493,7 +6543,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="259">
+    <row r="259" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A259" s="1" t="s">
         <v>428</v>
       </c>
@@ -6504,7 +6554,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="260">
+    <row r="260" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A260" s="1" t="s">
         <v>430</v>
       </c>
@@ -6515,7 +6565,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="261">
+    <row r="261" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A261" s="1" t="s">
         <v>432</v>
       </c>
@@ -6526,7 +6576,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="262">
+    <row r="262" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A262" s="1" t="s">
         <v>434</v>
       </c>
@@ -6537,7 +6587,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="263">
+    <row r="263" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A263" s="1" t="s">
         <v>434</v>
       </c>
@@ -6548,7 +6598,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="264">
+    <row r="264" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A264" s="1" t="s">
         <v>437</v>
       </c>
@@ -6559,7 +6609,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="265">
+    <row r="265" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A265" s="1" t="s">
         <v>439</v>
       </c>
@@ -6570,7 +6620,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="266">
+    <row r="266" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A266" s="1" t="s">
         <v>441</v>
       </c>
@@ -6581,7 +6631,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="267">
+    <row r="267" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A267" s="1" t="s">
         <v>443</v>
       </c>
@@ -6592,7 +6642,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="268">
+    <row r="268" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A268" s="1" t="s">
         <v>445</v>
       </c>
@@ -6603,7 +6653,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="269">
+    <row r="269" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A269" s="1" t="s">
         <v>445</v>
       </c>
@@ -6614,7 +6664,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="270">
+    <row r="270" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A270" s="1" t="s">
         <v>448</v>
       </c>
@@ -6625,7 +6675,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="271">
+    <row r="271" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A271" s="1" t="s">
         <v>450</v>
       </c>
@@ -6636,7 +6686,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="272">
+    <row r="272" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A272" s="1" t="s">
         <v>452</v>
       </c>
@@ -6647,7 +6697,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="273">
+    <row r="273" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A273" s="1" t="s">
         <v>454</v>
       </c>
@@ -6658,7 +6708,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="274">
+    <row r="274" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A274" s="1" t="s">
         <v>291</v>
       </c>
@@ -6669,7 +6719,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="275">
+    <row r="275" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A275" s="1" t="s">
         <v>457</v>
       </c>
@@ -6680,7 +6730,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="276">
+    <row r="276" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A276" s="1" t="s">
         <v>459</v>
       </c>
@@ -6691,7 +6741,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="277">
+    <row r="277" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A277" s="1" t="s">
         <v>461</v>
       </c>
@@ -6702,7 +6752,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="278">
+    <row r="278" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A278" s="1" t="s">
         <v>463</v>
       </c>
@@ -6713,7 +6763,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="279">
+    <row r="279" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A279" s="1" t="s">
         <v>98</v>
       </c>
@@ -6724,7 +6774,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="280">
+    <row r="280" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A280" s="1" t="s">
         <v>466</v>
       </c>
@@ -6735,7 +6785,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="281">
+    <row r="281" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A281" s="1" t="s">
         <v>66</v>
       </c>
@@ -6746,7 +6796,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="282">
+    <row r="282" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A282" s="1" t="s">
         <v>469</v>
       </c>
@@ -6757,7 +6807,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="283">
+    <row r="283" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A283" s="1" t="s">
         <v>396</v>
       </c>
@@ -6768,7 +6818,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="284">
+    <row r="284" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A284" s="1" t="s">
         <v>472</v>
       </c>
@@ -6779,7 +6829,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="285">
+    <row r="285" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A285" s="1" t="s">
         <v>474</v>
       </c>
@@ -6790,7 +6840,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="286">
+    <row r="286" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A286" s="1" t="s">
         <v>476</v>
       </c>
@@ -6801,7 +6851,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="287">
+    <row r="287" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A287" s="1" t="s">
         <v>478</v>
       </c>
@@ -6812,7 +6862,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="288">
+    <row r="288" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A288" s="1" t="s">
         <v>480</v>
       </c>
@@ -6823,7 +6873,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="289">
+    <row r="289" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A289" s="1" t="s">
         <v>482</v>
       </c>
@@ -6834,7 +6884,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="290">
+    <row r="290" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A290" s="1" t="s">
         <v>484</v>
       </c>
@@ -6845,7 +6895,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="291">
+    <row r="291" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A291" s="1" t="s">
         <v>486</v>
       </c>
@@ -6856,7 +6906,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="292">
+    <row r="292" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A292" s="1" t="s">
         <v>486</v>
       </c>
@@ -6867,7 +6917,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="293">
+    <row r="293" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A293" s="1" t="s">
         <v>486</v>
       </c>
@@ -6878,7 +6928,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="294">
+    <row r="294" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A294" s="1" t="s">
         <v>486</v>
       </c>
@@ -6889,7 +6939,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="295">
+    <row r="295" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A295" s="1" t="s">
         <v>297</v>
       </c>
@@ -6900,7 +6950,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="296">
+    <row r="296" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A296" s="1" t="s">
         <v>53</v>
       </c>
@@ -6911,7 +6961,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="297">
+    <row r="297" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A297" s="1" t="s">
         <v>53</v>
       </c>
@@ -6922,7 +6972,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="298">
+    <row r="298" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A298" s="1" t="s">
         <v>494</v>
       </c>
@@ -6933,7 +6983,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="299">
+    <row r="299" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A299" s="1" t="s">
         <v>496</v>
       </c>
@@ -6944,7 +6994,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="300">
+    <row r="300" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A300" s="1" t="s">
         <v>496</v>
       </c>
@@ -6955,7 +7005,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="301">
+    <row r="301" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A301" s="1" t="s">
         <v>499</v>
       </c>
@@ -6966,7 +7016,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="302">
+    <row r="302" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A302" s="1" t="s">
         <v>501</v>
       </c>
@@ -6977,7 +7027,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="303">
+    <row r="303" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A303" s="1" t="s">
         <v>503</v>
       </c>
@@ -6988,7 +7038,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="304">
+    <row r="304" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A304" s="1" t="s">
         <v>408</v>
       </c>
@@ -6999,7 +7049,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="305">
+    <row r="305" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A305" s="1" t="s">
         <v>506</v>
       </c>
@@ -7010,7 +7060,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="306">
+    <row r="306" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A306" s="1" t="s">
         <v>508</v>
       </c>
@@ -7021,7 +7071,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="307">
+    <row r="307" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A307" s="1" t="s">
         <v>508</v>
       </c>
@@ -7032,7 +7082,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="308">
+    <row r="308" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A308" s="1" t="s">
         <v>511</v>
       </c>
@@ -7043,7 +7093,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="309">
+    <row r="309" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A309" s="1" t="s">
         <v>513</v>
       </c>
@@ -7054,7 +7104,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="310">
+    <row r="310" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A310" s="1" t="s">
         <v>515</v>
       </c>
@@ -7065,7 +7115,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="311">
+    <row r="311" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A311" s="1" t="s">
         <v>517</v>
       </c>
@@ -7076,7 +7126,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="312">
+    <row r="312" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A312" s="1" t="s">
         <v>519</v>
       </c>
@@ -7087,7 +7137,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="313">
+    <row r="313" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A313" s="1" t="s">
         <v>521</v>
       </c>
@@ -7098,7 +7148,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="314">
+    <row r="314" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A314" s="1" t="s">
         <v>523</v>
       </c>
@@ -7109,7 +7159,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="315">
+    <row r="315" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A315" s="1" t="s">
         <v>525</v>
       </c>
@@ -7120,7 +7170,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="316">
+    <row r="316" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A316" s="1" t="s">
         <v>527</v>
       </c>
@@ -7131,7 +7181,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="317">
+    <row r="317" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A317" s="1" t="s">
         <v>529</v>
       </c>
@@ -7142,7 +7192,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="318">
+    <row r="318" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A318" s="1" t="s">
         <v>531</v>
       </c>
@@ -7153,7 +7203,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="319">
+    <row r="319" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A319" s="1" t="s">
         <v>533</v>
       </c>
@@ -7164,7 +7214,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="320">
+    <row r="320" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A320" s="1" t="s">
         <v>51</v>
       </c>
@@ -7175,7 +7225,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="321">
+    <row r="321" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A321" s="1" t="s">
         <v>536</v>
       </c>
@@ -7186,7 +7236,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="322">
+    <row r="322" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A322" s="1" t="s">
         <v>538</v>
       </c>
@@ -7197,7 +7247,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="323">
+    <row r="323" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A323" s="1" t="s">
         <v>540</v>
       </c>
@@ -7208,7 +7258,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="324">
+    <row r="324" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A324" s="1" t="s">
         <v>542</v>
       </c>
@@ -7219,7 +7269,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="325">
+    <row r="325" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A325" s="1" t="s">
         <v>366</v>
       </c>
@@ -7230,7 +7280,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="326">
+    <row r="326" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A326" s="1" t="s">
         <v>544</v>
       </c>
@@ -7241,7 +7291,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="327">
+    <row r="327" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A327" s="1" t="s">
         <v>546</v>
       </c>
@@ -7252,7 +7302,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="328">
+    <row r="328" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A328" s="1" t="s">
         <v>548</v>
       </c>
@@ -7263,7 +7313,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="329">
+    <row r="329" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A329" s="1" t="s">
         <v>550</v>
       </c>
@@ -7274,7 +7324,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="330">
+    <row r="330" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A330" s="1" t="s">
         <v>550</v>
       </c>
@@ -7285,7 +7335,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="331">
+    <row r="331" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A331" s="1" t="s">
         <v>553</v>
       </c>
@@ -7296,7 +7346,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="332">
+    <row r="332" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A332" s="1" t="s">
         <v>553</v>
       </c>
@@ -7307,7 +7357,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="333">
+    <row r="333" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A333" s="1" t="s">
         <v>556</v>
       </c>
@@ -7318,7 +7368,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="334">
+    <row r="334" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A334" s="1" t="s">
         <v>558</v>
       </c>
@@ -7329,7 +7379,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="335">
+    <row r="335" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A335" s="1" t="s">
         <v>558</v>
       </c>
@@ -7340,7 +7390,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="336">
+    <row r="336" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A336" s="1" t="s">
         <v>561</v>
       </c>
@@ -7351,7 +7401,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="337">
+    <row r="337" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A337" s="1" t="s">
         <v>561</v>
       </c>
@@ -7362,7 +7412,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="338">
+    <row r="338" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A338" s="1" t="s">
         <v>561</v>
       </c>
@@ -7373,7 +7423,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="339">
+    <row r="339" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A339" s="1" t="s">
         <v>565</v>
       </c>
@@ -7384,7 +7434,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="340">
+    <row r="340" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A340" s="1" t="s">
         <v>565</v>
       </c>
@@ -7395,7 +7445,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="341">
+    <row r="341" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A341" s="1" t="s">
         <v>568</v>
       </c>
@@ -7406,7 +7456,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="342">
+    <row r="342" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A342" s="1" t="s">
         <v>570</v>
       </c>
@@ -7417,7 +7467,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="343">
+    <row r="343" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A343" s="1" t="s">
         <v>570</v>
       </c>
@@ -7428,7 +7478,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="344">
+    <row r="344" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A344" s="1" t="s">
         <v>573</v>
       </c>
@@ -7439,7 +7489,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="345">
+    <row r="345" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A345" s="1" t="s">
         <v>573</v>
       </c>
@@ -7450,7 +7500,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="346">
+    <row r="346" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A346" s="1" t="s">
         <v>576</v>
       </c>
@@ -7461,7 +7511,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="347">
+    <row r="347" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A347" s="1" t="s">
         <v>578</v>
       </c>
@@ -7472,7 +7522,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="348">
+    <row r="348" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A348" s="1" t="s">
         <v>580</v>
       </c>
@@ -7483,7 +7533,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="349">
+    <row r="349" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A349" s="1" t="s">
         <v>582</v>
       </c>
@@ -7494,7 +7544,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="350">
+    <row r="350" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A350" s="1" t="s">
         <v>584</v>
       </c>
@@ -7505,7 +7555,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="351">
+    <row r="351" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A351" s="1" t="s">
         <v>586</v>
       </c>
@@ -7516,7 +7566,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="352">
+    <row r="352" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A352" s="1" t="s">
         <v>570</v>
       </c>
@@ -7527,7 +7577,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="353">
+    <row r="353" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A353" s="1" t="s">
         <v>589</v>
       </c>
@@ -7538,7 +7588,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="354">
+    <row r="354" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A354" s="1" t="s">
         <v>591</v>
       </c>
@@ -7549,7 +7599,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="355">
+    <row r="355" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A355" s="1" t="s">
         <v>591</v>
       </c>
@@ -7560,7 +7610,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="356">
+    <row r="356" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A356" s="1" t="s">
         <v>594</v>
       </c>
@@ -7571,7 +7621,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="357">
+    <row r="357" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A357" s="1" t="s">
         <v>596</v>
       </c>
@@ -7582,7 +7632,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="358">
+    <row r="358" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A358" s="1" t="s">
         <v>316</v>
       </c>
@@ -7593,7 +7643,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="359">
+    <row r="359" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A359" s="1" t="s">
         <v>599</v>
       </c>
@@ -7604,7 +7654,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="360">
+    <row r="360" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A360" s="1" t="s">
         <v>601</v>
       </c>
@@ -7615,7 +7665,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="361">
+    <row r="361" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A361" s="1" t="s">
         <v>603</v>
       </c>
@@ -7626,7 +7676,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="362">
+    <row r="362" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A362" s="1" t="s">
         <v>605</v>
       </c>
@@ -7637,7 +7687,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="363">
+    <row r="363" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A363" s="1" t="s">
         <v>607</v>
       </c>
@@ -7648,7 +7698,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="364">
+    <row r="364" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A364" s="1" t="s">
         <v>609</v>
       </c>
@@ -7659,7 +7709,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="365">
+    <row r="365" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A365" s="1" t="s">
         <v>611</v>
       </c>
@@ -7670,7 +7720,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="366">
+    <row r="366" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A366" s="1" t="s">
         <v>613</v>
       </c>
@@ -7681,7 +7731,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="367">
+    <row r="367" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A367" s="1" t="s">
         <v>197</v>
       </c>
@@ -7692,7 +7742,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="368">
+    <row r="368" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A368" s="1" t="s">
         <v>197</v>
       </c>
@@ -7703,7 +7753,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="369">
+    <row r="369" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A369" s="1" t="s">
         <v>617</v>
       </c>
@@ -7714,7 +7764,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="370">
+    <row r="370" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A370" s="1" t="s">
         <v>197</v>
       </c>
@@ -7725,7 +7775,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="371">
+    <row r="371" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A371" s="1" t="s">
         <v>197</v>
       </c>
@@ -7736,7 +7786,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="372">
+    <row r="372" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A372" s="1" t="s">
         <v>621</v>
       </c>
@@ -7747,7 +7797,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="373">
+    <row r="373" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A373" s="1" t="s">
         <v>623</v>
       </c>
@@ -7758,7 +7808,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="374">
+    <row r="374" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A374" s="1" t="s">
         <v>625</v>
       </c>
@@ -7769,7 +7819,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="375">
+    <row r="375" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A375" s="1" t="s">
         <v>197</v>
       </c>
@@ -7780,7 +7830,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="376">
+    <row r="376" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A376" s="1" t="s">
         <v>628</v>
       </c>
@@ -7791,7 +7841,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="377">
+    <row r="377" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A377" s="1" t="s">
         <v>197</v>
       </c>
@@ -7802,7 +7852,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="378">
+    <row r="378" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A378" s="1" t="s">
         <v>631</v>
       </c>
@@ -7813,7 +7863,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="379">
+    <row r="379" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A379" s="1" t="s">
         <v>633</v>
       </c>
@@ -7824,7 +7874,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="380">
+    <row r="380" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A380" s="1" t="s">
         <v>576</v>
       </c>
@@ -7835,7 +7885,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="381">
+    <row r="381" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A381" s="1" t="s">
         <v>636</v>
       </c>
@@ -7846,7 +7896,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="382">
+    <row r="382" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A382" s="1" t="s">
         <v>638</v>
       </c>
@@ -7857,7 +7907,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="383">
+    <row r="383" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A383" s="1" t="s">
         <v>640</v>
       </c>
@@ -7868,7 +7918,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="384">
+    <row r="384" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A384" s="1" t="s">
         <v>640</v>
       </c>
@@ -7879,7 +7929,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="385">
+    <row r="385" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A385" s="1" t="s">
         <v>643</v>
       </c>
@@ -7890,7 +7940,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="386">
+    <row r="386" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A386" s="1" t="s">
         <v>645</v>
       </c>
@@ -7901,7 +7951,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="387">
+    <row r="387" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A387" s="1" t="s">
         <v>647</v>
       </c>
@@ -7912,7 +7962,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="388">
+    <row r="388" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A388" s="1" t="s">
         <v>649</v>
       </c>
@@ -7923,7 +7973,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="389">
+    <row r="389" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A389" s="1" t="s">
         <v>651</v>
       </c>
@@ -7934,7 +7984,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="390">
+    <row r="390" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A390" s="1" t="s">
         <v>653</v>
       </c>
@@ -7945,7 +7995,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="391">
+    <row r="391" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A391" s="1" t="s">
         <v>32</v>
       </c>
@@ -7956,7 +8006,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="392">
+    <row r="392" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A392" s="1" t="s">
         <v>32</v>
       </c>
@@ -7967,7 +8017,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="393">
+    <row r="393" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A393" s="1" t="s">
         <v>657</v>
       </c>
@@ -7978,7 +8028,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="394">
+    <row r="394" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A394" s="1" t="s">
         <v>659</v>
       </c>
@@ -7989,7 +8039,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="395">
+    <row r="395" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A395" s="1" t="s">
         <v>659</v>
       </c>
@@ -8000,7 +8050,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="396">
+    <row r="396" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A396" s="1" t="s">
         <v>62</v>
       </c>
@@ -8011,7 +8061,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="397">
+    <row r="397" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A397" s="1" t="s">
         <v>62</v>
       </c>
@@ -8022,7 +8072,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="398">
+    <row r="398" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A398" s="1" t="s">
         <v>664</v>
       </c>
@@ -8033,7 +8083,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="399">
+    <row r="399" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A399" s="1" t="s">
         <v>78</v>
       </c>
@@ -8044,7 +8094,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="400">
+    <row r="400" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A400" s="1" t="s">
         <v>667</v>
       </c>
@@ -8055,7 +8105,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="401">
+    <row r="401" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A401" s="1" t="s">
         <v>62</v>
       </c>
@@ -8066,7 +8116,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="402">
+    <row r="402" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A402" s="1" t="s">
         <v>670</v>
       </c>
@@ -8077,7 +8127,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="403">
+    <row r="403" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A403" s="1" t="s">
         <v>672</v>
       </c>
@@ -8088,7 +8138,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="404">
+    <row r="404" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A404" s="1" t="s">
         <v>297</v>
       </c>
@@ -8099,7 +8149,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="405">
+    <row r="405" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A405" s="1" t="s">
         <v>94</v>
       </c>
@@ -8110,7 +8160,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="406">
+    <row r="406" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A406" s="1" t="s">
         <v>35</v>
       </c>
@@ -8121,7 +8171,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="407">
+    <row r="407" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A407" s="1" t="s">
         <v>677</v>
       </c>
@@ -8132,7 +8182,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="408">
+    <row r="408" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A408" s="1" t="s">
         <v>377</v>
       </c>
@@ -8143,7 +8193,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="409">
+    <row r="409" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A409" s="1" t="s">
         <v>680</v>
       </c>
@@ -8154,7 +8204,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="410">
+    <row r="410" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A410" s="1" t="s">
         <v>377</v>
       </c>
@@ -8165,7 +8215,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="411">
+    <row r="411" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A411" s="1" t="s">
         <v>683</v>
       </c>
@@ -8176,7 +8226,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="412">
+    <row r="412" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A412" s="1" t="s">
         <v>66</v>
       </c>
@@ -8187,18 +8237,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="413">
+    <row r="413" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A413" s="1" t="s">
         <v>377</v>
       </c>
       <c r="B413" s="1">
-        <v>1984.0</v>
+        <v>1984</v>
       </c>
       <c r="C413" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="414">
+    <row r="414" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A414" s="1" t="s">
         <v>62</v>
       </c>
@@ -8209,7 +8259,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="415">
+    <row r="415" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A415" s="1" t="s">
         <v>687</v>
       </c>
@@ -8220,7 +8270,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="416">
+    <row r="416" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A416" s="1" t="s">
         <v>689</v>
       </c>
@@ -8231,7 +8281,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="417">
+    <row r="417" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A417" s="1" t="s">
         <v>691</v>
       </c>
@@ -8242,7 +8292,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="418">
+    <row r="418" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A418" s="1" t="s">
         <v>693</v>
       </c>
@@ -8253,7 +8303,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="419">
+    <row r="419" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A419" s="1" t="s">
         <v>695</v>
       </c>
@@ -8264,7 +8314,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="420">
+    <row r="420" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A420" s="1" t="s">
         <v>697</v>
       </c>
@@ -8275,7 +8325,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="421">
+    <row r="421" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A421" s="1" t="s">
         <v>699</v>
       </c>
@@ -8286,7 +8336,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="422">
+    <row r="422" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A422" s="1" t="s">
         <v>533</v>
       </c>
@@ -8297,7 +8347,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="423">
+    <row r="423" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A423" s="1" t="s">
         <v>503</v>
       </c>
@@ -8308,7 +8358,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="424">
+    <row r="424" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A424" s="1" t="s">
         <v>703</v>
       </c>
@@ -8319,7 +8369,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="425">
+    <row r="425" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A425" s="1" t="s">
         <v>705</v>
       </c>
@@ -8330,7 +8380,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="426">
+    <row r="426" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A426" s="1" t="s">
         <v>707</v>
       </c>
@@ -8341,7 +8391,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="427">
+    <row r="427" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A427" s="1" t="s">
         <v>709</v>
       </c>
@@ -8352,7 +8402,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="428">
+    <row r="428" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A428" s="1" t="s">
         <v>709</v>
       </c>
@@ -8363,7 +8413,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="429">
+    <row r="429" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A429" s="1" t="s">
         <v>709</v>
       </c>
@@ -8374,7 +8424,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="430">
+    <row r="430" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A430" s="1" t="s">
         <v>709</v>
       </c>
@@ -8385,7 +8435,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="431">
+    <row r="431" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A431" s="1" t="s">
         <v>709</v>
       </c>
@@ -8396,7 +8446,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="432">
+    <row r="432" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A432" s="1" t="s">
         <v>709</v>
       </c>
@@ -8407,7 +8457,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="433">
+    <row r="433" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A433" s="1" t="s">
         <v>194</v>
       </c>
@@ -8418,7 +8468,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="434">
+    <row r="434" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A434" s="1" t="s">
         <v>716</v>
       </c>
@@ -8429,7 +8479,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="435">
+    <row r="435" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A435" s="1" t="s">
         <v>716</v>
       </c>
@@ -8440,7 +8490,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="436">
+    <row r="436" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A436" s="1" t="s">
         <v>719</v>
       </c>
@@ -8451,7 +8501,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="437">
+    <row r="437" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A437" s="1" t="s">
         <v>721</v>
       </c>
@@ -8462,7 +8512,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="438">
+    <row r="438" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A438" s="1" t="s">
         <v>461</v>
       </c>
@@ -8473,7 +8523,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="439">
+    <row r="439" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A439" s="1" t="s">
         <v>461</v>
       </c>
@@ -8484,7 +8534,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="440">
+    <row r="440" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A440" s="1" t="s">
         <v>194</v>
       </c>
@@ -8495,7 +8545,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="441">
+    <row r="441" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A441" s="1" t="s">
         <v>726</v>
       </c>
@@ -8506,7 +8556,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="442">
+    <row r="442" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A442" s="1" t="s">
         <v>728</v>
       </c>
@@ -8517,7 +8567,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="443">
+    <row r="443" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A443" s="1" t="s">
         <v>730</v>
       </c>
@@ -8528,7 +8578,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="444">
+    <row r="444" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A444" s="1" t="s">
         <v>732</v>
       </c>
@@ -8539,7 +8589,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="445">
+    <row r="445" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A445" s="1" t="s">
         <v>732</v>
       </c>
@@ -8550,7 +8600,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="446">
+    <row r="446" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A446" s="1" t="s">
         <v>732</v>
       </c>
@@ -8561,7 +8611,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="447">
+    <row r="447" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A447" s="1" t="s">
         <v>732</v>
       </c>
@@ -8572,7 +8622,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="448">
+    <row r="448" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A448" s="1" t="s">
         <v>732</v>
       </c>
@@ -8583,7 +8633,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="449">
+    <row r="449" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A449" s="1" t="s">
         <v>738</v>
       </c>
@@ -8594,7 +8644,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="450">
+    <row r="450" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A450" s="1" t="s">
         <v>740</v>
       </c>
@@ -8605,7 +8655,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="451">
+    <row r="451" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A451" s="1" t="s">
         <v>742</v>
       </c>
@@ -8616,7 +8666,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="452">
+    <row r="452" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A452" s="1" t="s">
         <v>197</v>
       </c>
@@ -8627,7 +8677,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="453">
+    <row r="453" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A453" s="1" t="s">
         <v>745</v>
       </c>
@@ -8638,7 +8688,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="454">
+    <row r="454" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A454" s="1" t="s">
         <v>747</v>
       </c>
@@ -8649,7 +8699,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="455">
+    <row r="455" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A455" s="1" t="s">
         <v>197</v>
       </c>
@@ -8660,7 +8710,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="456">
+    <row r="456" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A456" s="1" t="s">
         <v>750</v>
       </c>
@@ -8671,7 +8721,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="457">
+    <row r="457" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A457" s="1" t="s">
         <v>752</v>
       </c>
@@ -8682,7 +8732,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="458">
+    <row r="458" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A458" s="1" t="s">
         <v>754</v>
       </c>
@@ -8693,7 +8743,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="459">
+    <row r="459" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A459" s="1" t="s">
         <v>503</v>
       </c>
@@ -8704,7 +8754,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="460">
+    <row r="460" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A460" s="4" t="s">
         <v>757</v>
       </c>
@@ -8715,7 +8765,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="461">
+    <row r="461" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A461" s="1" t="s">
         <v>759</v>
       </c>
@@ -8726,7 +8776,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="462">
+    <row r="462" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A462" s="1" t="s">
         <v>759</v>
       </c>
@@ -8737,7 +8787,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="463">
+    <row r="463" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A463" s="1" t="s">
         <v>762</v>
       </c>
@@ -8748,7 +8798,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="464">
+    <row r="464" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A464" s="1" t="s">
         <v>764</v>
       </c>
@@ -8759,7 +8809,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="465">
+    <row r="465" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A465" s="1" t="s">
         <v>766</v>
       </c>
@@ -8770,7 +8820,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="466">
+    <row r="466" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A466" s="1" t="s">
         <v>766</v>
       </c>
@@ -8781,7 +8831,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="467">
+    <row r="467" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A467" s="1" t="s">
         <v>766</v>
       </c>
@@ -8792,7 +8842,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="468">
+    <row r="468" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A468" s="1" t="s">
         <v>766</v>
       </c>
@@ -8803,7 +8853,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="469">
+    <row r="469" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A469" s="1" t="s">
         <v>766</v>
       </c>
@@ -8814,7 +8864,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="470">
+    <row r="470" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A470" s="1" t="s">
         <v>766</v>
       </c>
@@ -8825,7 +8875,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="471">
+    <row r="471" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A471" s="1" t="s">
         <v>773</v>
       </c>
@@ -8836,7 +8886,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="472">
+    <row r="472" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A472" s="1" t="s">
         <v>775</v>
       </c>
@@ -8847,7 +8897,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="473">
+    <row r="473" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A473" s="1" t="s">
         <v>777</v>
       </c>
@@ -8858,7 +8908,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="474">
+    <row r="474" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A474" s="1" t="s">
         <v>779</v>
       </c>
@@ -8869,7 +8919,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="475">
+    <row r="475" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A475" s="1" t="s">
         <v>781</v>
       </c>
@@ -8880,7 +8930,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="476">
+    <row r="476" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A476" s="1" t="s">
         <v>783</v>
       </c>
@@ -8891,7 +8941,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="477">
+    <row r="477" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A477" s="1" t="s">
         <v>785</v>
       </c>
@@ -8902,7 +8952,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="478">
+    <row r="478" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A478" s="1" t="s">
         <v>39</v>
       </c>
@@ -8913,7 +8963,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="479">
+    <row r="479" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A479" s="1" t="s">
         <v>39</v>
       </c>
@@ -8924,7 +8974,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="480">
+    <row r="480" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A480" s="1" t="s">
         <v>39</v>
       </c>
@@ -8935,7 +8985,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="481">
+    <row r="481" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A481" s="1" t="s">
         <v>39</v>
       </c>
@@ -8946,7 +8996,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="482">
+    <row r="482" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A482" s="1" t="s">
         <v>791</v>
       </c>
@@ -8957,7 +9007,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="483">
+    <row r="483" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A483" s="1" t="s">
         <v>791</v>
       </c>
@@ -8968,7 +9018,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="484">
+    <row r="484" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A484" s="1" t="s">
         <v>791</v>
       </c>
@@ -8979,7 +9029,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="485">
+    <row r="485" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A485" s="1" t="s">
         <v>791</v>
       </c>
@@ -8990,7 +9040,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="486">
+    <row r="486" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A486" s="1" t="s">
         <v>791</v>
       </c>
@@ -9001,7 +9051,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="487">
+    <row r="487" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A487" s="1" t="s">
         <v>797</v>
       </c>
@@ -9012,7 +9062,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="488">
+    <row r="488" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A488" s="1" t="s">
         <v>125</v>
       </c>
@@ -9023,7 +9073,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="489">
+    <row r="489" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A489" s="1" t="s">
         <v>125</v>
       </c>
@@ -9034,7 +9084,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="490">
+    <row r="490" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A490" s="1" t="s">
         <v>125</v>
       </c>
@@ -9045,7 +9095,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="491">
+    <row r="491" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A491" s="1" t="s">
         <v>802</v>
       </c>
@@ -9056,7 +9106,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="492">
+    <row r="492" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A492" s="1" t="s">
         <v>804</v>
       </c>
@@ -9067,7 +9117,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="493">
+    <row r="493" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A493" s="1" t="s">
         <v>806</v>
       </c>
@@ -9078,7 +9128,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="494">
+    <row r="494" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A494" s="1" t="s">
         <v>55</v>
       </c>
@@ -9089,7 +9139,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="495">
+    <row r="495" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A495" s="1" t="s">
         <v>55</v>
       </c>
@@ -9100,7 +9150,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="496">
+    <row r="496" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A496" s="1" t="s">
         <v>810</v>
       </c>
@@ -9111,7 +9161,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="497">
+    <row r="497" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A497" s="1" t="s">
         <v>810</v>
       </c>
@@ -9122,7 +9172,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="498">
+    <row r="498" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A498" s="1" t="s">
         <v>810</v>
       </c>
@@ -9133,7 +9183,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="499">
+    <row r="499" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A499" s="1" t="s">
         <v>814</v>
       </c>
@@ -9144,7 +9194,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="500">
+    <row r="500" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A500" s="1" t="s">
         <v>816</v>
       </c>
@@ -9155,7 +9205,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="501">
+    <row r="501" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A501" s="1" t="s">
         <v>55</v>
       </c>
@@ -9166,7 +9216,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="502">
+    <row r="502" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A502" s="1" t="s">
         <v>819</v>
       </c>
@@ -9177,7 +9227,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="503">
+    <row r="503" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A503" s="1" t="s">
         <v>821</v>
       </c>
@@ -9188,7 +9238,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="504">
+    <row r="504" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A504" s="1" t="s">
         <v>823</v>
       </c>
@@ -9199,7 +9249,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="505">
+    <row r="505" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A505" s="1" t="s">
         <v>814</v>
       </c>
@@ -9210,7 +9260,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="506">
+    <row r="506" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A506" s="1" t="s">
         <v>814</v>
       </c>
@@ -9221,7 +9271,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="507">
+    <row r="507" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A507" s="1" t="s">
         <v>814</v>
       </c>
@@ -9232,7 +9282,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="508">
+    <row r="508" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A508" s="1" t="s">
         <v>628</v>
       </c>
@@ -9243,7 +9293,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="509">
+    <row r="509" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A509" s="1" t="s">
         <v>628</v>
       </c>
@@ -9254,7 +9304,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="510">
+    <row r="510" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A510" s="1" t="s">
         <v>628</v>
       </c>
@@ -9265,7 +9315,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="511">
+    <row r="511" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A511" s="1" t="s">
         <v>628</v>
       </c>
@@ -9276,7 +9326,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="512">
+    <row r="512" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A512" s="1" t="s">
         <v>832</v>
       </c>
@@ -9287,7 +9337,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="513">
+    <row r="513" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A513" s="1" t="s">
         <v>496</v>
       </c>
@@ -9298,7 +9348,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="514">
+    <row r="514" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A514" s="1" t="s">
         <v>496</v>
       </c>
@@ -9309,7 +9359,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="515">
+    <row r="515" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A515" s="1" t="s">
         <v>496</v>
       </c>
@@ -9320,7 +9370,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="516">
+    <row r="516" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A516" s="1" t="s">
         <v>836</v>
       </c>
@@ -9331,7 +9381,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="517">
+    <row r="517" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A517" s="1" t="s">
         <v>556</v>
       </c>
@@ -9342,7 +9392,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="518">
+    <row r="518" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A518" s="1" t="s">
         <v>839</v>
       </c>
@@ -9353,7 +9403,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="519">
+    <row r="519" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A519" s="1" t="s">
         <v>841</v>
       </c>
@@ -9364,7 +9414,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="520">
+    <row r="520" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A520" s="1" t="s">
         <v>843</v>
       </c>
@@ -9375,7 +9425,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="521">
+    <row r="521" spans="1:3" ht="13" x14ac:dyDescent="0.15">
       <c r="A521" s="1" t="s">
         <v>819</v>
       </c>
@@ -9386,19 +9436,63 @@
         <v>70</v>
       </c>
     </row>
-    <row r="522">
-      <c r="A522" s="1" t="s">
+    <row r="522" spans="1:3" ht="13" x14ac:dyDescent="0.15">
+      <c r="A522" s="5" t="s">
         <v>846</v>
       </c>
-      <c r="B522" s="1" t="s">
+      <c r="B522" s="5" t="s">
         <v>847</v>
       </c>
-      <c r="C522" s="1" t="s">
+      <c r="C522" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="523" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A523" s="5" t="s">
+        <v>848</v>
+      </c>
+      <c r="B523" s="5" t="s">
+        <v>849</v>
+      </c>
+      <c r="C523" s="5" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="524" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A524" s="5" t="s">
+        <v>850</v>
+      </c>
+      <c r="B524" s="5" t="s">
+        <v>851</v>
+      </c>
+      <c r="C524" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="525" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A525" s="5" t="s">
+        <v>852</v>
+      </c>
+      <c r="B525" s="5" t="s">
+        <v>853</v>
+      </c>
+      <c r="C525" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="526" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A526" s="5" t="s">
+        <v>854</v>
+      </c>
+      <c r="B526" s="5" t="s">
+        <v>855</v>
+      </c>
+      <c r="C526" s="5" t="s">
         <v>70</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$C$508"/>
-  <drawing r:id="rId1"/>
+  <autoFilter ref="A1:C508" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Книги.xlsx
+++ b/Книги.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dmitrypotekhin/Downloads/dmpotekhin.github.io/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58AC6FE8-5FCE-3B4B-9F86-097CC3819155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02B342AC-36A9-8D4A-BEB8-D78346198B29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="16000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1574" uniqueCount="856">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1583" uniqueCount="861">
   <si>
     <t>Борис Акунин</t>
   </si>
@@ -2592,6 +2592,21 @@
   </si>
   <si>
     <t>Принципы Жизнь и работа</t>
+  </si>
+  <si>
+    <t>Дональд Трамп Мысли масштабно</t>
+  </si>
+  <si>
+    <t>Олег Самородний</t>
+  </si>
+  <si>
+    <t>Пол Пот Камбоджа - Империя на Костях?</t>
+  </si>
+  <si>
+    <t>Анна Леонуэнс</t>
+  </si>
+  <si>
+    <t>Путешествие в Сиам</t>
   </si>
 </sst>
 </file>
@@ -2894,7 +2909,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:U526"/>
+  <dimension ref="A1:U529"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -9491,6 +9506,39 @@
         <v>70</v>
       </c>
     </row>
+    <row r="527" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A527" s="5" t="s">
+        <v>548</v>
+      </c>
+      <c r="B527" s="5" t="s">
+        <v>856</v>
+      </c>
+      <c r="C527" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="528" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A528" s="5" t="s">
+        <v>857</v>
+      </c>
+      <c r="B528" s="5" t="s">
+        <v>858</v>
+      </c>
+      <c r="C528" s="5" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="529" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A529" s="5" t="s">
+        <v>859</v>
+      </c>
+      <c r="B529" s="5" t="s">
+        <v>860</v>
+      </c>
+      <c r="C529" s="5" t="s">
+        <v>169</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C508" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Книги.xlsx
+++ b/Книги.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dmitrypotekhin/Downloads/dmpotekhin.github.io/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02B342AC-36A9-8D4A-BEB8-D78346198B29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81C502F7-181D-2E43-A964-0355164D7B3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="16000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1583" uniqueCount="861">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1595" uniqueCount="868">
   <si>
     <t>Борис Акунин</t>
   </si>
@@ -2607,6 +2607,27 @@
   </si>
   <si>
     <t>Путешествие в Сиам</t>
+  </si>
+  <si>
+    <t>Ли Бао</t>
+  </si>
+  <si>
+    <t>Китайская Культурная Революция</t>
+  </si>
+  <si>
+    <t>Путешествие на Новую Гвинею</t>
+  </si>
+  <si>
+    <t>Николай Миклохо-Маклай</t>
+  </si>
+  <si>
+    <t>Собака на сене</t>
+  </si>
+  <si>
+    <t>Лопе де Вега</t>
+  </si>
+  <si>
+    <t>100 млн модель продаж</t>
   </si>
 </sst>
 </file>
@@ -2909,7 +2930,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:U529"/>
+  <dimension ref="A1:U533"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -9539,8 +9560,53 @@
         <v>169</v>
       </c>
     </row>
+    <row r="530" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A530" s="5" t="s">
+        <v>861</v>
+      </c>
+      <c r="B530" s="5" t="s">
+        <v>862</v>
+      </c>
+      <c r="C530" s="5" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="531" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A531" s="5" t="s">
+        <v>864</v>
+      </c>
+      <c r="B531" s="5" t="s">
+        <v>863</v>
+      </c>
+      <c r="C531" s="5" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="532" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A532" s="5" t="s">
+        <v>866</v>
+      </c>
+      <c r="B532" s="5" t="s">
+        <v>865</v>
+      </c>
+      <c r="C532" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="533" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A533" s="5" t="s">
+        <v>850</v>
+      </c>
+      <c r="B533" s="5" t="s">
+        <v>867</v>
+      </c>
+      <c r="C533" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C508" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/Книги.xlsx
+++ b/Книги.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dmitrypotekhin/Downloads/dmpotekhin.github.io/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81C502F7-181D-2E43-A964-0355164D7B3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B34B3BF-DAA1-C342-8367-4C0353E2D633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="16000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1595" uniqueCount="868">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="869">
   <si>
     <t>Борис Акунин</t>
   </si>
@@ -2628,6 +2628,9 @@
   </si>
   <si>
     <t>100 млн модель продаж</t>
+  </si>
+  <si>
+    <t>100 млн модель Лиды</t>
   </si>
 </sst>
 </file>
@@ -2930,7 +2933,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:U533"/>
+  <dimension ref="A1:U534"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -9604,6 +9607,17 @@
         <v>70</v>
       </c>
     </row>
+    <row r="534" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A534" s="5" t="s">
+        <v>850</v>
+      </c>
+      <c r="B534" s="5" t="s">
+        <v>868</v>
+      </c>
+      <c r="C534" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C508" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Книги.xlsx
+++ b/Книги.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dmitrypotekhin/Downloads/dmpotekhin.github.io/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B34B3BF-DAA1-C342-8367-4C0353E2D633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61823D8C-1C31-F046-8BAE-603A4BD136D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="16000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="869">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1604" uniqueCount="873">
   <si>
     <t>Борис Акунин</t>
   </si>
@@ -2631,6 +2631,18 @@
   </si>
   <si>
     <t>100 млн модель Лиды</t>
+  </si>
+  <si>
+    <t>Искусство видеть</t>
+  </si>
+  <si>
+    <t>Джон Бергер</t>
+  </si>
+  <si>
+    <t>Анастасия Постригай</t>
+  </si>
+  <si>
+    <t>Влюбиться в исскуство</t>
   </si>
 </sst>
 </file>
@@ -2933,7 +2945,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:U534"/>
+  <dimension ref="A1:U536"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -9618,6 +9630,28 @@
         <v>70</v>
       </c>
     </row>
+    <row r="535" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A535" s="5" t="s">
+        <v>870</v>
+      </c>
+      <c r="B535" s="5" t="s">
+        <v>869</v>
+      </c>
+      <c r="C535" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="536" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A536" s="5" t="s">
+        <v>871</v>
+      </c>
+      <c r="B536" s="5" t="s">
+        <v>872</v>
+      </c>
+      <c r="C536" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C508" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Книги.xlsx
+++ b/Книги.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dmitrypotekhin/Downloads/dmpotekhin.github.io/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E829B1BF-9092-4645-B30D-55663602AC00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF84D64C-7B01-C04F-AD4D-2F1AA0AFCADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="16000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Книги" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Книги!$A$1:$C$508</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Книги!$A$1:$C$506</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1641" uniqueCount="892">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1628" uniqueCount="892">
   <si>
     <t>Борис Акунин</t>
   </si>
@@ -146,9 +146,6 @@
   </si>
   <si>
     <t>Том Сойер</t>
-  </si>
-  <si>
-    <t>Трургенев</t>
   </si>
   <si>
     <t>Муму</t>
@@ -1634,9 +1631,6 @@
     <t>о Сахалин</t>
   </si>
   <si>
-    <t>Тругенев</t>
-  </si>
-  <si>
     <t>Дворянское гнездо</t>
   </si>
   <si>
@@ -2699,7 +2693,13 @@
     <t>Архипелаг гулаг</t>
   </si>
   <si>
-    <t>ы</t>
+    <t>Александр Бындю</t>
+  </si>
+  <si>
+    <t>Эрин Мейер</t>
+  </si>
+  <si>
+    <t>Elisabeth Hendrickson</t>
   </si>
 </sst>
 </file>
@@ -2717,17 +2717,20 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2998,7 +3001,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:U556"/>
+  <dimension ref="A1:U552"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -3749,10 +3752,10 @@
     </row>
     <row r="33" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>2</v>
@@ -3778,10 +3781,10 @@
     </row>
     <row r="34" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>2</v>
@@ -3807,10 +3810,10 @@
     </row>
     <row r="35" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>2</v>
@@ -3836,10 +3839,10 @@
     </row>
     <row r="36" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>2</v>
@@ -3865,10 +3868,10 @@
     </row>
     <row r="37" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>2</v>
@@ -3894,10 +3897,10 @@
     </row>
     <row r="38" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>2</v>
@@ -3923,10 +3926,10 @@
     </row>
     <row r="39" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>2</v>
@@ -3952,10 +3955,10 @@
     </row>
     <row r="40" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>2</v>
@@ -3981,10 +3984,10 @@
     </row>
     <row r="41" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>2</v>
@@ -4010,10 +4013,10 @@
     </row>
     <row r="42" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>2</v>
@@ -4039,10 +4042,10 @@
     </row>
     <row r="43" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>2</v>
@@ -4068,10 +4071,10 @@
     </row>
     <row r="44" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>2</v>
@@ -4097,10 +4100,10 @@
     </row>
     <row r="45" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>2</v>
@@ -4126,10 +4129,10 @@
     </row>
     <row r="46" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>2</v>
@@ -4155,10 +4158,10 @@
     </row>
     <row r="47" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>2</v>
@@ -4184,13 +4187,13 @@
     </row>
     <row r="48" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B48" s="1" t="s">
-        <v>69</v>
-      </c>
       <c r="C48" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
@@ -4213,10 +4216,10 @@
     </row>
     <row r="49" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>2</v>
@@ -4242,10 +4245,10 @@
     </row>
     <row r="50" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>74</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>2</v>
@@ -4271,10 +4274,10 @@
     </row>
     <row r="51" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>2</v>
@@ -4300,10 +4303,10 @@
     </row>
     <row r="52" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>2</v>
@@ -4329,10 +4332,10 @@
     </row>
     <row r="53" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>2</v>
@@ -4358,10 +4361,10 @@
     </row>
     <row r="54" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>79</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>2</v>
@@ -4387,10 +4390,10 @@
     </row>
     <row r="55" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>2</v>
@@ -4416,10 +4419,10 @@
     </row>
     <row r="56" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>2</v>
@@ -4427,10 +4430,10 @@
     </row>
     <row r="57" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>2</v>
@@ -4438,10 +4441,10 @@
     </row>
     <row r="58" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>2</v>
@@ -4449,10 +4452,10 @@
     </row>
     <row r="59" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>2</v>
@@ -4460,10 +4463,10 @@
     </row>
     <row r="60" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>2</v>
@@ -4471,10 +4474,10 @@
     </row>
     <row r="61" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>2</v>
@@ -4482,10 +4485,10 @@
     </row>
     <row r="62" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>2</v>
@@ -4493,10 +4496,10 @@
     </row>
     <row r="63" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>2</v>
@@ -4504,10 +4507,10 @@
     </row>
     <row r="64" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>2</v>
@@ -4515,10 +4518,10 @@
     </row>
     <row r="65" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>2</v>
@@ -4526,10 +4529,10 @@
     </row>
     <row r="66" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>2</v>
@@ -4537,10 +4540,10 @@
     </row>
     <row r="67" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>2</v>
@@ -4548,10 +4551,10 @@
     </row>
     <row r="68" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>2</v>
@@ -4559,10 +4562,10 @@
     </row>
     <row r="69" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>95</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>2</v>
@@ -4570,10 +4573,10 @@
     </row>
     <row r="70" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>2</v>
@@ -4584,7 +4587,7 @@
         <v>35</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>2</v>
@@ -4592,10 +4595,10 @@
     </row>
     <row r="72" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>99</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>2</v>
@@ -4603,10 +4606,10 @@
     </row>
     <row r="73" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B73" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>101</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>2</v>
@@ -4614,153 +4617,153 @@
     </row>
     <row r="74" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B74" s="1" t="s">
-        <v>103</v>
-      </c>
       <c r="C74" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="C75" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="C76" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B79" s="1" t="s">
-        <v>112</v>
-      </c>
       <c r="C79" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B80" s="1" t="s">
-        <v>114</v>
-      </c>
       <c r="C80" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B83" s="1" t="s">
-        <v>118</v>
-      </c>
       <c r="C83" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B84" s="1" t="s">
-        <v>120</v>
-      </c>
       <c r="C84" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B85" s="1" t="s">
-        <v>122</v>
-      </c>
       <c r="C85" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B86" s="1" t="s">
-        <v>124</v>
-      </c>
       <c r="C86" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>126</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>2</v>
@@ -4768,208 +4771,208 @@
     </row>
     <row r="88" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B88" s="1" t="s">
-        <v>128</v>
-      </c>
       <c r="C88" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B89" s="1" t="s">
-        <v>130</v>
-      </c>
       <c r="C89" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B90" s="1" t="s">
-        <v>132</v>
-      </c>
       <c r="C90" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B91" s="1" t="s">
-        <v>134</v>
-      </c>
       <c r="C91" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="92" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>137</v>
-      </c>
       <c r="C93" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B94" s="1" t="s">
-        <v>139</v>
-      </c>
       <c r="C94" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B95" s="1" t="s">
-        <v>141</v>
-      </c>
       <c r="C95" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B96" s="1" t="s">
-        <v>143</v>
-      </c>
       <c r="C96" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B97" s="1" t="s">
-        <v>145</v>
-      </c>
       <c r="C97" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>147</v>
-      </c>
       <c r="C98" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B99" s="1" t="s">
-        <v>149</v>
-      </c>
       <c r="C99" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="100" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B100" s="1" t="s">
-        <v>151</v>
-      </c>
       <c r="C100" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B101" s="1" t="s">
-        <v>153</v>
-      </c>
       <c r="C101" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>155</v>
-      </c>
       <c r="C102" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>157</v>
-      </c>
       <c r="C103" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="105" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="106" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>161</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>2</v>
@@ -4977,241 +4980,241 @@
     </row>
     <row r="107" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="1" t="s">
-        <v>160</v>
+        <v>889</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="108" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="C108" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="109" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="1" t="s">
-        <v>163</v>
+        <v>891</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="110" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="1" t="s">
-        <v>163</v>
+        <v>890</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="111" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B111" s="1" t="s">
+      <c r="C111" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="112" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>171</v>
-      </c>
       <c r="C112" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="113" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B113" s="1" t="s">
-        <v>173</v>
-      </c>
       <c r="C113" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="114" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B114" s="1" t="s">
-        <v>175</v>
-      </c>
       <c r="C114" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="115" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>177</v>
-      </c>
       <c r="C115" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="116" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="117" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="118" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A118" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="119" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="120" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>183</v>
-      </c>
       <c r="C120" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="121" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="122" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A122" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B122" s="1" t="s">
-        <v>186</v>
-      </c>
       <c r="C122" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="123" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B123" s="1" t="s">
-        <v>188</v>
-      </c>
       <c r="C123" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="124" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="125" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="126" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A126" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>192</v>
-      </c>
       <c r="C126" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="127" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A127" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="128" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A128" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>194</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>195</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>2</v>
@@ -5219,87 +5222,87 @@
     </row>
     <row r="129" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A129" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="130" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A130" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B130" s="1" t="s">
-        <v>198</v>
-      </c>
       <c r="C130" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="131" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A131" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B131" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="C131" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="132" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A132" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="133" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A133" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="B133" s="1" t="s">
-        <v>203</v>
-      </c>
       <c r="C133" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="134" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A134" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B134" s="1" t="s">
-        <v>205</v>
-      </c>
       <c r="C134" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="135" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A135" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B135" s="1" t="s">
-        <v>207</v>
-      </c>
       <c r="C135" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="136" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A136" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>208</v>
-      </c>
-      <c r="B136" s="1" t="s">
-        <v>209</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>2</v>
@@ -5307,10 +5310,10 @@
     </row>
     <row r="137" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A137" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>210</v>
-      </c>
-      <c r="B137" s="1" t="s">
-        <v>211</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>2</v>
@@ -5318,10 +5321,10 @@
     </row>
     <row r="138" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A138" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>2</v>
@@ -5329,10 +5332,10 @@
     </row>
     <row r="139" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A139" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="B139" s="1" t="s">
-        <v>214</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>2</v>
@@ -5340,10 +5343,10 @@
     </row>
     <row r="140" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A140" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>215</v>
-      </c>
-      <c r="B140" s="1" t="s">
-        <v>216</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>2</v>
@@ -5351,21 +5354,21 @@
     </row>
     <row r="141" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A141" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B141" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B141" s="1" t="s">
-        <v>218</v>
-      </c>
       <c r="C141" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="142" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A142" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B142" s="1" t="s">
         <v>219</v>
-      </c>
-      <c r="B142" s="1" t="s">
-        <v>220</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>2</v>
@@ -5373,21 +5376,21 @@
     </row>
     <row r="143" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A143" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="B143" s="1" t="s">
-        <v>222</v>
-      </c>
       <c r="C143" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="144" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A144" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B144" s="1" t="s">
         <v>223</v>
-      </c>
-      <c r="B144" s="1" t="s">
-        <v>224</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>2</v>
@@ -5395,87 +5398,87 @@
     </row>
     <row r="145" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A145" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B145" s="1" t="s">
-        <v>226</v>
-      </c>
       <c r="C145" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="146" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A146" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B146" s="1" t="s">
-        <v>228</v>
-      </c>
       <c r="C146" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="147" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A147" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="148" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A148" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="149" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A149" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B149" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B149" s="1" t="s">
-        <v>232</v>
-      </c>
       <c r="C149" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="150" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A150" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="151" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A151" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>235</v>
-      </c>
       <c r="C151" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="152" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A152" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B152" s="1" t="s">
         <v>236</v>
-      </c>
-      <c r="B152" s="1" t="s">
-        <v>237</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>2</v>
@@ -5483,10 +5486,10 @@
     </row>
     <row r="153" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A153" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B153" s="1" t="s">
         <v>238</v>
-      </c>
-      <c r="B153" s="1" t="s">
-        <v>239</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>2</v>
@@ -5494,10 +5497,10 @@
     </row>
     <row r="154" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A154" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B154" s="1" t="s">
         <v>240</v>
-      </c>
-      <c r="B154" s="1" t="s">
-        <v>241</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>2</v>
@@ -5505,76 +5508,76 @@
     </row>
     <row r="155" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A155" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="B155" s="1" t="s">
-        <v>243</v>
-      </c>
       <c r="C155" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="156" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A156" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="B156" s="1" t="s">
-        <v>245</v>
-      </c>
       <c r="C156" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="157" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A157" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="158" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A158" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="159" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A159" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="160" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A160" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B160" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B160" s="1" t="s">
-        <v>250</v>
-      </c>
       <c r="C160" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="161" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A161" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B161" s="1" t="s">
         <v>251</v>
-      </c>
-      <c r="B161" s="1" t="s">
-        <v>252</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>2</v>
@@ -5582,21 +5585,21 @@
     </row>
     <row r="162" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A162" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B162" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="B162" s="1" t="s">
-        <v>254</v>
-      </c>
       <c r="C162" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="163" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A163" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B163" s="1" t="s">
         <v>255</v>
-      </c>
-      <c r="B163" s="1" t="s">
-        <v>256</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>2</v>
@@ -5604,10 +5607,10 @@
     </row>
     <row r="164" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A164" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>2</v>
@@ -5615,98 +5618,98 @@
     </row>
     <row r="165" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A165" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="166" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A166" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B166" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B166" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="C166" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="167" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A167" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="168" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A168" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B168" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B168" s="1" t="s">
-        <v>263</v>
-      </c>
       <c r="C168" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="169" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A169" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="170" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A170" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="171" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A171" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="172" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A172" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="173" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A173" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>268</v>
-      </c>
-      <c r="B173" s="1" t="s">
-        <v>269</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>2</v>
@@ -5714,43 +5717,43 @@
     </row>
     <row r="174" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A174" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B174" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B174" s="1" t="s">
-        <v>271</v>
-      </c>
       <c r="C174" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="175" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A175" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B175" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="B175" s="1" t="s">
-        <v>273</v>
-      </c>
       <c r="C175" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="176" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A176" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B176" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="B176" s="1" t="s">
-        <v>275</v>
-      </c>
       <c r="C176" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="177" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A177" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B177" s="1" t="s">
         <v>276</v>
-      </c>
-      <c r="B177" s="1" t="s">
-        <v>277</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>2</v>
@@ -5758,21 +5761,21 @@
     </row>
     <row r="178" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A178" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="179" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A179" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B179" s="1" t="s">
         <v>279</v>
-      </c>
-      <c r="B179" s="1" t="s">
-        <v>280</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>2</v>
@@ -5780,21 +5783,21 @@
     </row>
     <row r="180" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A180" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B180" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="B180" s="1" t="s">
-        <v>282</v>
-      </c>
       <c r="C180" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="181" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A181" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>2</v>
@@ -5802,21 +5805,21 @@
     </row>
     <row r="182" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A182" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B182" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B182" s="1" t="s">
-        <v>285</v>
-      </c>
       <c r="C182" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="183" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A183" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B183" s="1" t="s">
         <v>286</v>
-      </c>
-      <c r="B183" s="1" t="s">
-        <v>287</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>2</v>
@@ -5824,32 +5827,32 @@
     </row>
     <row r="184" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A184" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B184" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="B184" s="1" t="s">
-        <v>289</v>
-      </c>
       <c r="C184" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="185" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A185" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="186" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A186" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B186" s="1" t="s">
         <v>291</v>
-      </c>
-      <c r="B186" s="1" t="s">
-        <v>292</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>2</v>
@@ -5857,10 +5860,10 @@
     </row>
     <row r="187" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A187" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B187" s="1" t="s">
         <v>293</v>
-      </c>
-      <c r="B187" s="1" t="s">
-        <v>294</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>2</v>
@@ -5868,494 +5871,494 @@
     </row>
     <row r="188" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A188" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B188" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B188" s="1" t="s">
-        <v>296</v>
-      </c>
       <c r="C188" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="189" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A189" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B189" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="B189" s="1" t="s">
-        <v>298</v>
-      </c>
       <c r="C189" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="190" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A190" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B190" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="B190" s="1" t="s">
-        <v>300</v>
-      </c>
       <c r="C190" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="191" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A191" s="1" t="s">
-        <v>47</v>
+        <v>300</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>50</v>
+        <v>301</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>2</v>
+        <v>107</v>
       </c>
     </row>
     <row r="192" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A192" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="193" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A193" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>108</v>
+        <v>69</v>
       </c>
     </row>
     <row r="194" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A194" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B194" s="1" t="s">
         <v>306</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="195" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A195" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="196" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A196" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
     </row>
     <row r="197" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A197" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>108</v>
+        <v>69</v>
       </c>
     </row>
     <row r="198" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A198" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
     </row>
     <row r="199" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A199" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="200" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A200" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="201" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A201" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="202" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A202" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="B202" s="1" t="s">
         <v>321</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="203" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A203" s="1" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>108</v>
+        <v>69</v>
       </c>
     </row>
     <row r="204" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A204" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
     </row>
     <row r="205" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A205" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="206" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A206" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="207" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A207" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>108</v>
+        <v>69</v>
       </c>
     </row>
     <row r="208" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A208" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>70</v>
+        <v>2</v>
       </c>
     </row>
     <row r="209" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A209" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B209" s="1" t="s">
         <v>334</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="210" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A210" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="211" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A211" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="212" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A212" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="213" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A213" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>70</v>
+        <v>168</v>
       </c>
     </row>
     <row r="214" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A214" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>169</v>
+        <v>107</v>
       </c>
     </row>
     <row r="215" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A215" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>108</v>
+        <v>168</v>
       </c>
     </row>
     <row r="216" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A216" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="217" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A217" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="218" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A218" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="219" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A219" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>169</v>
+        <v>69</v>
       </c>
     </row>
     <row r="220" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A220" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="221" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A221" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>70</v>
+        <v>2</v>
       </c>
     </row>
     <row r="222" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A222" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="223" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A223" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>70</v>
+        <v>2</v>
       </c>
     </row>
     <row r="224" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A224" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="225" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A225" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="226" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A226" s="1" t="s">
-        <v>366</v>
+        <v>261</v>
       </c>
       <c r="B226" s="1" t="s">
         <v>367</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="227" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A227" s="1" t="s">
-        <v>262</v>
+        <v>368</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>70</v>
+        <v>2</v>
       </c>
     </row>
     <row r="228" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A228" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="229" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A229" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>70</v>
+        <v>168</v>
       </c>
     </row>
     <row r="230" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A230" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="231" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A231" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>169</v>
+        <v>2</v>
       </c>
     </row>
     <row r="232" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A232" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>2</v>
@@ -6363,120 +6366,120 @@
     </row>
     <row r="233" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A233" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>2</v>
+        <v>168</v>
       </c>
     </row>
     <row r="234" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A234" s="1" t="s">
-        <v>381</v>
+      <c r="A234" s="3" t="s">
+        <v>128</v>
       </c>
       <c r="B234" s="1" t="s">
         <v>382</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="235" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A235" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B235" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="236" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A236" s="3" t="s">
-        <v>129</v>
+        <v>384</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="237" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A237" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="238" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A238" s="3" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="239" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A239" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="240" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A240" s="3" t="s">
-        <v>391</v>
+        <v>349</v>
       </c>
       <c r="B240" s="1" t="s">
         <v>392</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="241" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A241" s="3" t="s">
-        <v>350</v>
+        <v>393</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="242" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A242" s="3" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>169</v>
+        <v>2</v>
       </c>
     </row>
     <row r="243" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A243" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>2</v>
@@ -6484,10 +6487,10 @@
     </row>
     <row r="244" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A244" s="3" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>2</v>
@@ -6495,43 +6498,43 @@
     </row>
     <row r="245" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A245" s="3" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="246" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A246" s="3" t="s">
-        <v>402</v>
+      <c r="A246" s="1" t="s">
+        <v>403</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="247" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A247" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>70</v>
+        <v>2</v>
       </c>
     </row>
     <row r="248" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A248" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>2</v>
@@ -6539,65 +6542,65 @@
     </row>
     <row r="249" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A249" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="250" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A250" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="251" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A251" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="252" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A252" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="253" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A253" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>70</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A254" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>2</v>
@@ -6605,43 +6608,43 @@
     </row>
     <row r="255" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A255" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="256" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A256" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="257" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A257" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="258" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A258" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>2</v>
@@ -6649,10 +6652,10 @@
     </row>
     <row r="259" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A259" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>2</v>
@@ -6660,10 +6663,10 @@
     </row>
     <row r="260" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A260" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>2</v>
@@ -6671,230 +6674,230 @@
     </row>
     <row r="261" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A261" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="262" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A262" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B262" s="1" t="s">
         <v>435</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>70</v>
+        <v>168</v>
       </c>
     </row>
     <row r="263" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A263" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>169</v>
+        <v>2</v>
       </c>
     </row>
     <row r="264" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A264" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="265" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A265" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="266" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A266" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>70</v>
+        <v>2</v>
       </c>
     </row>
     <row r="267" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A267" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>2</v>
+        <v>168</v>
       </c>
     </row>
     <row r="268" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A268" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B268" s="1" t="s">
         <v>446</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="269" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A269" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>169</v>
+        <v>69</v>
       </c>
     </row>
     <row r="270" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A270" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="271" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A271" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>70</v>
+        <v>2</v>
       </c>
     </row>
     <row r="272" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A272" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>2</v>
+        <v>168</v>
       </c>
     </row>
     <row r="273" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A273" s="1" t="s">
-        <v>454</v>
+        <v>290</v>
       </c>
       <c r="B273" s="1" t="s">
         <v>455</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>169</v>
+        <v>2</v>
       </c>
     </row>
     <row r="274" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A274" s="1" t="s">
-        <v>291</v>
+        <v>456</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="275" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A275" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>70</v>
+        <v>168</v>
       </c>
     </row>
     <row r="276" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A276" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>169</v>
+        <v>2</v>
       </c>
     </row>
     <row r="277" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A277" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>2</v>
+        <v>168</v>
       </c>
     </row>
     <row r="278" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A278" s="1" t="s">
-        <v>463</v>
+        <v>97</v>
       </c>
       <c r="B278" s="1" t="s">
         <v>464</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>169</v>
+        <v>2</v>
       </c>
     </row>
     <row r="279" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A279" s="1" t="s">
-        <v>98</v>
+        <v>465</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="280" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A280" s="1" t="s">
-        <v>466</v>
+        <v>65</v>
       </c>
       <c r="B280" s="1" t="s">
         <v>467</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>70</v>
+        <v>2</v>
       </c>
     </row>
     <row r="281" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A281" s="1" t="s">
-        <v>66</v>
+        <v>468</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>2</v>
@@ -6902,7 +6905,7 @@
     </row>
     <row r="282" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A282" s="1" t="s">
-        <v>469</v>
+        <v>395</v>
       </c>
       <c r="B282" s="1" t="s">
         <v>470</v>
@@ -6913,10 +6916,10 @@
     </row>
     <row r="283" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A283" s="1" t="s">
-        <v>396</v>
+        <v>471</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>2</v>
@@ -6924,10 +6927,10 @@
     </row>
     <row r="284" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A284" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>2</v>
@@ -6935,153 +6938,153 @@
     </row>
     <row r="285" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A285" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>2</v>
+        <v>107</v>
       </c>
     </row>
     <row r="286" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A286" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>108</v>
+        <v>168</v>
       </c>
     </row>
     <row r="287" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A287" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="288" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A288" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="289" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A289" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="290" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A290" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>169</v>
+        <v>2</v>
       </c>
     </row>
     <row r="291" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A291" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B291" s="1" t="s">
         <v>487</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>2</v>
+        <v>168</v>
       </c>
     </row>
     <row r="292" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A292" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B292" s="1" t="s">
         <v>488</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="293" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A293" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B293" s="1" t="s">
         <v>489</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="294" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A294" s="1" t="s">
-        <v>486</v>
+        <v>296</v>
       </c>
       <c r="B294" s="1" t="s">
         <v>490</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>169</v>
+        <v>69</v>
       </c>
     </row>
     <row r="295" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A295" s="1" t="s">
-        <v>297</v>
+        <v>52</v>
       </c>
       <c r="B295" s="1" t="s">
         <v>491</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>70</v>
+        <v>2</v>
       </c>
     </row>
     <row r="296" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A296" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B296" s="1" t="s">
         <v>492</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>2</v>
+        <v>168</v>
       </c>
     </row>
     <row r="297" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A297" s="1" t="s">
-        <v>53</v>
+        <v>493</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>169</v>
+        <v>2</v>
       </c>
     </row>
     <row r="298" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A298" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>2</v>
@@ -7089,7 +7092,7 @@
     </row>
     <row r="299" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A299" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B299" s="1" t="s">
         <v>497</v>
@@ -7100,40 +7103,40 @@
     </row>
     <row r="300" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A300" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="301" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A301" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="302" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A302" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C302" s="1" t="s">
-        <v>70</v>
+        <v>2</v>
       </c>
     </row>
     <row r="303" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A303" s="1" t="s">
-        <v>503</v>
+        <v>407</v>
       </c>
       <c r="B303" s="1" t="s">
         <v>504</v>
@@ -7144,10 +7147,10 @@
     </row>
     <row r="304" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A304" s="1" t="s">
-        <v>408</v>
+        <v>505</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>2</v>
@@ -7155,76 +7158,76 @@
     </row>
     <row r="305" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A305" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C305" s="1" t="s">
-        <v>2</v>
+        <v>168</v>
       </c>
     </row>
     <row r="306" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A306" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B306" s="1" t="s">
         <v>509</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>169</v>
+        <v>107</v>
       </c>
     </row>
     <row r="307" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A307" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C307" s="1" t="s">
-        <v>108</v>
+        <v>2</v>
       </c>
     </row>
     <row r="308" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A308" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C308" s="1" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="309" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A309" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>70</v>
+        <v>168</v>
       </c>
     </row>
     <row r="310" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A310" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C310" s="1" t="s">
-        <v>169</v>
+        <v>2</v>
       </c>
     </row>
     <row r="311" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A311" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>2</v>
@@ -7232,10 +7235,10 @@
     </row>
     <row r="312" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A312" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>2</v>
@@ -7243,84 +7246,84 @@
     </row>
     <row r="313" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A313" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="314" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A314" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C314" s="1" t="s">
-        <v>70</v>
+        <v>168</v>
       </c>
     </row>
     <row r="315" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A315" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C315" s="1" t="s">
-        <v>169</v>
+        <v>69</v>
       </c>
     </row>
     <row r="316" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A316" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C316" s="1" t="s">
-        <v>70</v>
+        <v>168</v>
       </c>
     </row>
     <row r="317" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A317" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>169</v>
+        <v>69</v>
       </c>
     </row>
     <row r="318" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A318" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="319" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A319" s="1" t="s">
-        <v>533</v>
+        <v>50</v>
       </c>
       <c r="B319" s="1" t="s">
         <v>534</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>70</v>
+        <v>2</v>
       </c>
     </row>
     <row r="320" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A320" s="1" t="s">
-        <v>51</v>
+        <v>427</v>
       </c>
       <c r="B320" s="1" t="s">
         <v>535</v>
@@ -7337,7 +7340,7 @@
         <v>537</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>2</v>
+        <v>168</v>
       </c>
     </row>
     <row r="322" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
@@ -7348,7 +7351,7 @@
         <v>539</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="323" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
@@ -7359,7 +7362,7 @@
         <v>541</v>
       </c>
       <c r="C323" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="324" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
@@ -7370,40 +7373,40 @@
         <v>543</v>
       </c>
       <c r="C324" s="1" t="s">
-        <v>169</v>
+        <v>2</v>
       </c>
     </row>
     <row r="325" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A325" s="1" t="s">
-        <v>366</v>
+        <v>544</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>367</v>
+        <v>545</v>
       </c>
       <c r="C325" s="1" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
     </row>
     <row r="326" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A326" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C326" s="1" t="s">
-        <v>2</v>
+        <v>168</v>
       </c>
     </row>
     <row r="327" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A327" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C327" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="328" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
@@ -7411,54 +7414,54 @@
         <v>548</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C328" s="1" t="s">
-        <v>169</v>
+        <v>107</v>
       </c>
     </row>
     <row r="329" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A329" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C329" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="330" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A330" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C330" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="331" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A331" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C331" s="1" t="s">
-        <v>108</v>
+        <v>69</v>
       </c>
     </row>
     <row r="332" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A332" s="1" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C332" s="1" t="s">
-        <v>108</v>
+        <v>2</v>
       </c>
     </row>
     <row r="333" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
@@ -7466,87 +7469,87 @@
         <v>556</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C333" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="334" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A334" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C334" s="1" t="s">
-        <v>2</v>
+        <v>107</v>
       </c>
     </row>
     <row r="335" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A335" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
     </row>
     <row r="336" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A336" s="1" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B336" s="1" t="s">
         <v>562</v>
       </c>
       <c r="C336" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="337" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A337" s="1" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C337" s="1" t="s">
-        <v>108</v>
+        <v>168</v>
       </c>
     </row>
     <row r="338" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A338" s="1" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C338" s="1" t="s">
-        <v>108</v>
+        <v>69</v>
       </c>
     </row>
     <row r="339" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A339" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C339" s="1" t="s">
-        <v>169</v>
+        <v>69</v>
       </c>
     </row>
     <row r="340" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A340" s="1" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C340" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="341" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
@@ -7554,131 +7557,131 @@
         <v>568</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C341" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="342" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A342" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C342" s="1" t="s">
-        <v>70</v>
+        <v>2</v>
       </c>
     </row>
     <row r="343" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A343" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B343" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C343" s="1" t="s">
-        <v>70</v>
+        <v>168</v>
       </c>
     </row>
     <row r="344" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A344" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C344" s="1" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="345" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A345" s="1" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C345" s="1" t="s">
-        <v>169</v>
+        <v>69</v>
       </c>
     </row>
     <row r="346" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A346" s="1" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C346" s="1" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
     </row>
     <row r="347" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A347" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C347" s="1" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
     </row>
     <row r="348" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A348" s="1" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C348" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="349" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A349" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C349" s="1" t="s">
-        <v>108</v>
+        <v>69</v>
       </c>
     </row>
     <row r="350" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A350" s="1" t="s">
-        <v>584</v>
+        <v>568</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C350" s="1" t="s">
-        <v>108</v>
+        <v>69</v>
       </c>
     </row>
     <row r="351" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A351" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C351" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="352" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A352" s="1" t="s">
-        <v>570</v>
+        <v>589</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C352" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="353" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
@@ -7686,315 +7689,315 @@
         <v>589</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C353" s="1" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
     </row>
     <row r="354" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A354" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C354" s="1" t="s">
-        <v>70</v>
+        <v>2</v>
       </c>
     </row>
     <row r="355" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A355" s="1" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="B355" s="1" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="C355" s="1" t="s">
-        <v>108</v>
+        <v>2</v>
       </c>
     </row>
     <row r="356" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A356" s="1" t="s">
-        <v>594</v>
+        <v>315</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C356" s="1" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="357" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A357" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C357" s="1" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="358" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A358" s="1" t="s">
-        <v>316</v>
+        <v>599</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="C358" s="1" t="s">
-        <v>70</v>
+        <v>2</v>
       </c>
     </row>
     <row r="359" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A359" s="1" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B359" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C359" s="1" t="s">
-        <v>70</v>
+        <v>2</v>
       </c>
     </row>
     <row r="360" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A360" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C360" s="1" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="361" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A361" s="1" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B361" s="1" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C361" s="1" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="362" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A362" s="1" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C362" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="363" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A363" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B363" s="1" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C363" s="1" t="s">
-        <v>70</v>
+        <v>2</v>
       </c>
     </row>
     <row r="364" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A364" s="1" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C364" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="365" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A365" s="1" t="s">
-        <v>611</v>
+        <v>196</v>
       </c>
       <c r="B365" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C365" s="1" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="366" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A366" s="1" t="s">
-        <v>613</v>
+        <v>196</v>
       </c>
       <c r="B366" s="1" t="s">
         <v>614</v>
       </c>
       <c r="C366" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="367" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A367" s="1" t="s">
-        <v>197</v>
+        <v>615</v>
       </c>
       <c r="B367" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C367" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="368" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A368" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C368" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="369" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A369" s="1" t="s">
-        <v>617</v>
+        <v>196</v>
       </c>
       <c r="B369" s="1" t="s">
         <v>618</v>
       </c>
       <c r="C369" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="370" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A370" s="1" t="s">
-        <v>197</v>
+        <v>619</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C370" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="371" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A371" s="1" t="s">
-        <v>197</v>
+        <v>621</v>
       </c>
       <c r="B371" s="1" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="C371" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="372" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A372" s="1" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="C372" s="1" t="s">
-        <v>70</v>
+        <v>2</v>
       </c>
     </row>
     <row r="373" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A373" s="1" t="s">
-        <v>623</v>
+        <v>196</v>
       </c>
       <c r="B373" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C373" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="374" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A374" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C374" s="1" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="375" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A375" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B375" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C375" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="376" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A376" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C376" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="377" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A377" s="1" t="s">
-        <v>197</v>
+        <v>631</v>
       </c>
       <c r="B377" s="1" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="C377" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="378" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A378" s="1" t="s">
-        <v>631</v>
+        <v>574</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C378" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="379" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A379" s="1" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B379" s="1" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C379" s="1" t="s">
-        <v>70</v>
+        <v>2</v>
       </c>
     </row>
     <row r="380" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A380" s="1" t="s">
-        <v>576</v>
+        <v>636</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C380" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="381" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A381" s="1" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B381" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>2</v>
@@ -8005,18 +8008,18 @@
         <v>638</v>
       </c>
       <c r="B382" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C382" s="1" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
     </row>
     <row r="383" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A383" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B383" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>2</v>
@@ -8024,21 +8027,21 @@
     </row>
     <row r="384" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A384" s="1" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="B384" s="1" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="C384" s="1" t="s">
-        <v>108</v>
+        <v>69</v>
       </c>
     </row>
     <row r="385" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A385" s="1" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="B385" s="1" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>2</v>
@@ -8046,21 +8049,21 @@
     </row>
     <row r="386" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A386" s="1" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C386" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="387" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A387" s="1" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B387" s="1" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>2</v>
@@ -8068,21 +8071,21 @@
     </row>
     <row r="388" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A388" s="1" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="C388" s="1" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
     </row>
     <row r="389" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A389" s="1" t="s">
-        <v>651</v>
+        <v>32</v>
       </c>
       <c r="B389" s="1" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>2</v>
@@ -8090,21 +8093,21 @@
     </row>
     <row r="390" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A390" s="1" t="s">
-        <v>653</v>
+        <v>32</v>
       </c>
       <c r="B390" s="1" t="s">
         <v>654</v>
       </c>
       <c r="C390" s="1" t="s">
-        <v>108</v>
+        <v>2</v>
       </c>
     </row>
     <row r="391" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A391" s="1" t="s">
-        <v>32</v>
+        <v>655</v>
       </c>
       <c r="B391" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>2</v>
@@ -8112,13 +8115,13 @@
     </row>
     <row r="392" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A392" s="1" t="s">
-        <v>32</v>
+        <v>657</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="C392" s="1" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="393" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
@@ -8126,40 +8129,40 @@
         <v>657</v>
       </c>
       <c r="B393" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C393" s="1" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="394" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A394" s="1" t="s">
-        <v>659</v>
+        <v>61</v>
       </c>
       <c r="B394" s="1" t="s">
         <v>660</v>
       </c>
       <c r="C394" s="1" t="s">
-        <v>70</v>
+        <v>2</v>
       </c>
     </row>
     <row r="395" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A395" s="1" t="s">
-        <v>659</v>
+        <v>61</v>
       </c>
       <c r="B395" s="1" t="s">
         <v>661</v>
       </c>
       <c r="C395" s="1" t="s">
-        <v>70</v>
+        <v>2</v>
       </c>
     </row>
     <row r="396" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A396" s="1" t="s">
-        <v>62</v>
+        <v>662</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>2</v>
@@ -8167,10 +8170,10 @@
     </row>
     <row r="397" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A397" s="1" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B397" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>2</v>
@@ -8178,10 +8181,10 @@
     </row>
     <row r="398" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A398" s="1" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>2</v>
@@ -8189,10 +8192,10 @@
     </row>
     <row r="399" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A399" s="1" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="B399" s="1" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C399" s="1" t="s">
         <v>2</v>
@@ -8200,10 +8203,10 @@
     </row>
     <row r="400" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A400" s="1" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C400" s="1" t="s">
         <v>2</v>
@@ -8211,10 +8214,10 @@
     </row>
     <row r="401" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A401" s="1" t="s">
-        <v>62</v>
+        <v>670</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="C401" s="1" t="s">
         <v>2</v>
@@ -8222,18 +8225,18 @@
     </row>
     <row r="402" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A402" s="1" t="s">
-        <v>670</v>
+        <v>296</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C402" s="1" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="403" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A403" s="1" t="s">
-        <v>672</v>
+        <v>93</v>
       </c>
       <c r="B403" s="1" t="s">
         <v>673</v>
@@ -8244,32 +8247,32 @@
     </row>
     <row r="404" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A404" s="1" t="s">
-        <v>297</v>
+        <v>35</v>
       </c>
       <c r="B404" s="1" t="s">
         <v>674</v>
       </c>
       <c r="C404" s="1" t="s">
-        <v>70</v>
+        <v>2</v>
       </c>
     </row>
     <row r="405" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A405" s="1" t="s">
-        <v>94</v>
+        <v>675</v>
       </c>
       <c r="B405" s="1" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C405" s="1" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="406" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A406" s="1" t="s">
-        <v>35</v>
+        <v>376</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C406" s="1" t="s">
         <v>2</v>
@@ -8277,21 +8280,21 @@
     </row>
     <row r="407" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A407" s="1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B407" s="1" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C407" s="1" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
     </row>
     <row r="408" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A408" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C408" s="1" t="s">
         <v>2</v>
@@ -8299,21 +8302,21 @@
     </row>
     <row r="409" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A409" s="1" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B409" s="1" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C409" s="1" t="s">
-        <v>108</v>
+        <v>2</v>
       </c>
     </row>
     <row r="410" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A410" s="1" t="s">
-        <v>377</v>
+        <v>65</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C410" s="1" t="s">
         <v>2</v>
@@ -8321,10 +8324,10 @@
     </row>
     <row r="411" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A411" s="1" t="s">
-        <v>683</v>
-      </c>
-      <c r="B411" s="1" t="s">
-        <v>684</v>
+        <v>376</v>
+      </c>
+      <c r="B411" s="1">
+        <v>1984</v>
       </c>
       <c r="C411" s="1" t="s">
         <v>2</v>
@@ -8332,10 +8335,10 @@
     </row>
     <row r="412" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A412" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C412" s="1" t="s">
         <v>2</v>
@@ -8343,10 +8346,10 @@
     </row>
     <row r="413" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A413" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="B413" s="1">
-        <v>1984</v>
+        <v>685</v>
+      </c>
+      <c r="B413" s="1" t="s">
+        <v>686</v>
       </c>
       <c r="C413" s="1" t="s">
         <v>2</v>
@@ -8354,10 +8357,10 @@
     </row>
     <row r="414" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A414" s="1" t="s">
-        <v>62</v>
+        <v>687</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="C414" s="1" t="s">
         <v>2</v>
@@ -8365,21 +8368,21 @@
     </row>
     <row r="415" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A415" s="1" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="B415" s="1" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="C415" s="1" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="416" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A416" s="1" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="C416" s="1" t="s">
         <v>2</v>
@@ -8387,21 +8390,21 @@
     </row>
     <row r="417" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A417" s="1" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="B417" s="1" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="C417" s="1" t="s">
-        <v>70</v>
+        <v>2</v>
       </c>
     </row>
     <row r="418" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A418" s="1" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="C418" s="1" t="s">
         <v>2</v>
@@ -8409,79 +8412,79 @@
     </row>
     <row r="419" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A419" s="1" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="B419" s="1" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="C419" s="1" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="420" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A420" s="1" t="s">
-        <v>697</v>
+        <v>532</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C420" s="1" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="421" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A421" s="1" t="s">
-        <v>699</v>
+        <v>502</v>
       </c>
       <c r="B421" s="1" t="s">
         <v>700</v>
       </c>
       <c r="C421" s="1" t="s">
-        <v>70</v>
+        <v>2</v>
       </c>
     </row>
     <row r="422" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A422" s="1" t="s">
-        <v>533</v>
+        <v>701</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C422" s="1" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
     </row>
     <row r="423" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A423" s="1" t="s">
-        <v>503</v>
+        <v>703</v>
       </c>
       <c r="B423" s="1" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="C423" s="1" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="424" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A424" s="1" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="C424" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="425" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A425" s="1" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="B425" s="1" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="C425" s="1" t="s">
-        <v>70</v>
+        <v>2</v>
       </c>
     </row>
     <row r="426" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
@@ -8489,15 +8492,15 @@
         <v>707</v>
       </c>
       <c r="B426" s="1" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C426" s="1" t="s">
-        <v>108</v>
+        <v>2</v>
       </c>
     </row>
     <row r="427" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A427" s="1" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B427" s="1" t="s">
         <v>710</v>
@@ -8508,7 +8511,7 @@
     </row>
     <row r="428" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A428" s="1" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B428" s="1" t="s">
         <v>711</v>
@@ -8519,7 +8522,7 @@
     </row>
     <row r="429" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A429" s="1" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B429" s="1" t="s">
         <v>712</v>
@@ -8530,7 +8533,7 @@
     </row>
     <row r="430" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A430" s="1" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B430" s="1" t="s">
         <v>713</v>
@@ -8541,65 +8544,65 @@
     </row>
     <row r="431" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A431" s="1" t="s">
-        <v>709</v>
+        <v>193</v>
       </c>
       <c r="B431" s="1" t="s">
-        <v>714</v>
+        <v>208</v>
       </c>
       <c r="C431" s="1" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="432" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A432" s="1" t="s">
-        <v>709</v>
+        <v>714</v>
       </c>
       <c r="B432" s="1" t="s">
         <v>715</v>
       </c>
       <c r="C432" s="1" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="433" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A433" s="1" t="s">
-        <v>194</v>
+        <v>714</v>
       </c>
       <c r="B433" s="1" t="s">
-        <v>209</v>
+        <v>716</v>
       </c>
       <c r="C433" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="434" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A434" s="1" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B434" s="1" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C434" s="1" t="s">
-        <v>70</v>
+        <v>2</v>
       </c>
     </row>
     <row r="435" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A435" s="1" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="B435" s="1" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="C435" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="436" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A436" s="1" t="s">
-        <v>719</v>
+        <v>460</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C436" s="1" t="s">
         <v>2</v>
@@ -8607,18 +8610,18 @@
     </row>
     <row r="437" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A437" s="1" t="s">
-        <v>721</v>
+        <v>460</v>
       </c>
       <c r="B437" s="1" t="s">
         <v>722</v>
       </c>
       <c r="C437" s="1" t="s">
-        <v>70</v>
+        <v>2</v>
       </c>
     </row>
     <row r="438" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A438" s="1" t="s">
-        <v>461</v>
+        <v>193</v>
       </c>
       <c r="B438" s="1" t="s">
         <v>723</v>
@@ -8629,46 +8632,46 @@
     </row>
     <row r="439" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A439" s="1" t="s">
-        <v>461</v>
+        <v>724</v>
       </c>
       <c r="B439" s="1" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C439" s="1" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="440" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A440" s="1" t="s">
-        <v>194</v>
+        <v>726</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="C440" s="1" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="441" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A441" s="1" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="B441" s="1" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="C441" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="442" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A442" s="1" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="B442" s="1" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="C442" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="443" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
@@ -8676,227 +8679,227 @@
         <v>730</v>
       </c>
       <c r="B443" s="1" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C443" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="444" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A444" s="1" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="B444" s="1" t="s">
         <v>733</v>
       </c>
       <c r="C444" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="445" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A445" s="1" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="B445" s="1" t="s">
         <v>734</v>
       </c>
       <c r="C445" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="446" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A446" s="1" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="B446" s="1" t="s">
         <v>735</v>
       </c>
       <c r="C446" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="447" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A447" s="1" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="B447" s="1" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C447" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="448" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A448" s="1" t="s">
-        <v>732</v>
+        <v>738</v>
       </c>
       <c r="B448" s="1" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C448" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="449" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A449" s="1" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="B449" s="1" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="C449" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="450" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A450" s="1" t="s">
-        <v>740</v>
+        <v>196</v>
       </c>
       <c r="B450" s="1" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C450" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="451" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A451" s="1" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B451" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C451" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="452" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A452" s="1" t="s">
-        <v>197</v>
+        <v>745</v>
       </c>
       <c r="B452" s="1" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="C452" s="1" t="s">
-        <v>70</v>
+        <v>2</v>
       </c>
     </row>
     <row r="453" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A453" s="1" t="s">
-        <v>745</v>
+        <v>196</v>
       </c>
       <c r="B453" s="1" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C453" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="454" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A454" s="1" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B454" s="1" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C454" s="1" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="455" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A455" s="1" t="s">
-        <v>197</v>
+        <v>750</v>
       </c>
       <c r="B455" s="1" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="C455" s="1" t="s">
-        <v>70</v>
+        <v>2</v>
       </c>
     </row>
     <row r="456" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A456" s="1" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="B456" s="1" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="C456" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="457" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A457" s="1" t="s">
-        <v>752</v>
+        <v>502</v>
       </c>
       <c r="B457" s="1" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="C457" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="458" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A458" s="1" t="s">
-        <v>754</v>
+      <c r="A458" s="4" t="s">
+        <v>755</v>
       </c>
       <c r="B458" s="1" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C458" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="459" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A459" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="B459" s="1" t="s">
-        <v>756</v>
+        <v>757</v>
+      </c>
+      <c r="B459" s="4" t="s">
+        <v>758</v>
       </c>
       <c r="C459" s="1" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="460" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A460" s="4" t="s">
+      <c r="A460" s="1" t="s">
         <v>757</v>
       </c>
       <c r="B460" s="1" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C460" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="461" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A461" s="1" t="s">
-        <v>759</v>
-      </c>
-      <c r="B461" s="4" t="s">
         <v>760</v>
       </c>
+      <c r="B461" s="1" t="s">
+        <v>761</v>
+      </c>
       <c r="C461" s="1" t="s">
-        <v>70</v>
+        <v>2</v>
       </c>
     </row>
     <row r="462" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A462" s="1" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="B462" s="1" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="C462" s="1" t="s">
-        <v>70</v>
+        <v>2</v>
       </c>
     </row>
     <row r="463" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A463" s="1" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="B463" s="1" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="C463" s="1" t="s">
         <v>2</v>
@@ -8907,7 +8910,7 @@
         <v>764</v>
       </c>
       <c r="B464" s="1" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C464" s="1" t="s">
         <v>2</v>
@@ -8915,7 +8918,7 @@
     </row>
     <row r="465" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A465" s="1" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B465" s="1" t="s">
         <v>767</v>
@@ -8926,7 +8929,7 @@
     </row>
     <row r="466" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A466" s="1" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B466" s="1" t="s">
         <v>768</v>
@@ -8937,7 +8940,7 @@
     </row>
     <row r="467" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A467" s="1" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B467" s="1" t="s">
         <v>769</v>
@@ -8948,7 +8951,7 @@
     </row>
     <row r="468" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A468" s="1" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B468" s="1" t="s">
         <v>770</v>
@@ -8959,87 +8962,87 @@
     </row>
     <row r="469" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A469" s="1" t="s">
-        <v>766</v>
+        <v>771</v>
       </c>
       <c r="B469" s="1" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C469" s="1" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="470" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A470" s="1" t="s">
-        <v>766</v>
+        <v>773</v>
       </c>
       <c r="B470" s="1" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="C470" s="1" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="471" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A471" s="1" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B471" s="1" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C471" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="472" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A472" s="1" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="B472" s="1" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="C472" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="473" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A473" s="1" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B473" s="1" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="C473" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="474" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A474" s="1" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="B474" s="1" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="C474" s="1" t="s">
-        <v>70</v>
+        <v>2</v>
       </c>
     </row>
     <row r="475" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A475" s="1" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="B475" s="1" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="C475" s="1" t="s">
-        <v>70</v>
+        <v>2</v>
       </c>
     </row>
     <row r="476" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A476" s="1" t="s">
-        <v>783</v>
+        <v>39</v>
       </c>
       <c r="B476" s="1" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C476" s="1" t="s">
         <v>2</v>
@@ -9047,7 +9050,7 @@
     </row>
     <row r="477" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A477" s="1" t="s">
-        <v>785</v>
+        <v>39</v>
       </c>
       <c r="B477" s="1" t="s">
         <v>786</v>
@@ -9080,10 +9083,10 @@
     </row>
     <row r="480" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A480" s="1" t="s">
-        <v>39</v>
+        <v>789</v>
       </c>
       <c r="B480" s="1" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C480" s="1" t="s">
         <v>2</v>
@@ -9091,10 +9094,10 @@
     </row>
     <row r="481" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A481" s="1" t="s">
-        <v>39</v>
+        <v>789</v>
       </c>
       <c r="B481" s="1" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C481" s="1" t="s">
         <v>2</v>
@@ -9102,7 +9105,7 @@
     </row>
     <row r="482" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A482" s="1" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="B482" s="1" t="s">
         <v>792</v>
@@ -9113,7 +9116,7 @@
     </row>
     <row r="483" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A483" s="1" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="B483" s="1" t="s">
         <v>793</v>
@@ -9124,7 +9127,7 @@
     </row>
     <row r="484" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A484" s="1" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="B484" s="1" t="s">
         <v>794</v>
@@ -9135,10 +9138,10 @@
     </row>
     <row r="485" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A485" s="1" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="B485" s="1" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C485" s="1" t="s">
         <v>2</v>
@@ -9146,10 +9149,10 @@
     </row>
     <row r="486" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A486" s="1" t="s">
-        <v>791</v>
+        <v>124</v>
       </c>
       <c r="B486" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="C486" s="1" t="s">
         <v>2</v>
@@ -9157,7 +9160,7 @@
     </row>
     <row r="487" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A487" s="1" t="s">
-        <v>797</v>
+        <v>124</v>
       </c>
       <c r="B487" s="1" t="s">
         <v>798</v>
@@ -9168,7 +9171,7 @@
     </row>
     <row r="488" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A488" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B488" s="1" t="s">
         <v>799</v>
@@ -9179,10 +9182,10 @@
     </row>
     <row r="489" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A489" s="1" t="s">
-        <v>125</v>
+        <v>800</v>
       </c>
       <c r="B489" s="1" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="C489" s="1" t="s">
         <v>2</v>
@@ -9190,10 +9193,10 @@
     </row>
     <row r="490" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A490" s="1" t="s">
-        <v>125</v>
+        <v>802</v>
       </c>
       <c r="B490" s="1" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="C490" s="1" t="s">
         <v>2</v>
@@ -9201,10 +9204,10 @@
     </row>
     <row r="491" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A491" s="1" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="B491" s="1" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C491" s="1" t="s">
         <v>2</v>
@@ -9212,10 +9215,10 @@
     </row>
     <row r="492" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A492" s="1" t="s">
-        <v>804</v>
+        <v>54</v>
       </c>
       <c r="B492" s="1" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C492" s="1" t="s">
         <v>2</v>
@@ -9223,7 +9226,7 @@
     </row>
     <row r="493" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A493" s="1" t="s">
-        <v>806</v>
+        <v>54</v>
       </c>
       <c r="B493" s="1" t="s">
         <v>807</v>
@@ -9234,10 +9237,10 @@
     </row>
     <row r="494" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A494" s="1" t="s">
-        <v>55</v>
+        <v>808</v>
       </c>
       <c r="B494" s="1" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C494" s="1" t="s">
         <v>2</v>
@@ -9245,10 +9248,10 @@
     </row>
     <row r="495" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A495" s="1" t="s">
-        <v>55</v>
+        <v>808</v>
       </c>
       <c r="B495" s="1" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C495" s="1" t="s">
         <v>2</v>
@@ -9256,7 +9259,7 @@
     </row>
     <row r="496" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A496" s="1" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="B496" s="1" t="s">
         <v>811</v>
@@ -9267,10 +9270,10 @@
     </row>
     <row r="497" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A497" s="1" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B497" s="1" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C497" s="1" t="s">
         <v>2</v>
@@ -9278,10 +9281,10 @@
     </row>
     <row r="498" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A498" s="1" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="B498" s="1" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="C498" s="1" t="s">
         <v>2</v>
@@ -9289,10 +9292,10 @@
     </row>
     <row r="499" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A499" s="1" t="s">
-        <v>814</v>
+        <v>54</v>
       </c>
       <c r="B499" s="1" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C499" s="1" t="s">
         <v>2</v>
@@ -9300,550 +9303,504 @@
     </row>
     <row r="500" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A500" s="1" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B500" s="1" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C500" s="1" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="501" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A501" s="1" t="s">
-        <v>55</v>
+        <v>819</v>
       </c>
       <c r="B501" s="1" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="C501" s="1" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="502" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A502" s="1" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="B502" s="1" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="C502" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="503" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A503" s="1" t="s">
-        <v>821</v>
+        <v>812</v>
       </c>
       <c r="B503" s="1" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C503" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="504" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A504" s="1" t="s">
-        <v>823</v>
+        <v>812</v>
       </c>
       <c r="B504" s="1" t="s">
         <v>824</v>
       </c>
       <c r="C504" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="505" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A505" s="1" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="B505" s="1" t="s">
         <v>825</v>
       </c>
       <c r="C505" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="506" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A506" s="1" t="s">
-        <v>814</v>
+        <v>626</v>
       </c>
       <c r="B506" s="1" t="s">
         <v>826</v>
       </c>
       <c r="C506" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="507" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A507" s="1" t="s">
-        <v>814</v>
+        <v>626</v>
       </c>
       <c r="B507" s="1" t="s">
         <v>827</v>
       </c>
       <c r="C507" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="508" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A508" s="1" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B508" s="1" t="s">
         <v>828</v>
       </c>
       <c r="C508" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="509" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A509" s="1" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B509" s="1" t="s">
         <v>829</v>
       </c>
       <c r="C509" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="510" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A510" s="1" t="s">
-        <v>628</v>
+        <v>830</v>
       </c>
       <c r="B510" s="1" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="C510" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="511" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A511" s="1" t="s">
-        <v>628</v>
+        <v>495</v>
       </c>
       <c r="B511" s="1" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C511" s="1" t="s">
-        <v>70</v>
+        <v>2</v>
       </c>
     </row>
     <row r="512" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A512" s="1" t="s">
-        <v>832</v>
+        <v>495</v>
       </c>
       <c r="B512" s="1" t="s">
         <v>833</v>
       </c>
       <c r="C512" s="1" t="s">
-        <v>70</v>
+        <v>2</v>
       </c>
     </row>
     <row r="513" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A513" s="1" t="s">
-        <v>496</v>
+        <v>834</v>
       </c>
       <c r="B513" s="1" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="C513" s="1" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="514" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A514" s="1" t="s">
-        <v>496</v>
+        <v>554</v>
       </c>
       <c r="B514" s="1" t="s">
-        <v>498</v>
+        <v>836</v>
       </c>
       <c r="C514" s="1" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="515" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A515" s="1" t="s">
-        <v>496</v>
+        <v>837</v>
       </c>
       <c r="B515" s="1" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="C515" s="1" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="516" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A516" s="1" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="B516" s="1" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="C516" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="517" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A517" s="1" t="s">
-        <v>556</v>
+        <v>841</v>
       </c>
       <c r="B517" s="1" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="C517" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="518" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A518" s="1" t="s">
-        <v>839</v>
+        <v>817</v>
       </c>
       <c r="B518" s="1" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="C518" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="519" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A519" s="1" t="s">
-        <v>841</v>
-      </c>
-      <c r="B519" s="1" t="s">
-        <v>842</v>
-      </c>
-      <c r="C519" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="520" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A520" s="1" t="s">
-        <v>843</v>
-      </c>
-      <c r="B520" s="1" t="s">
+      <c r="A519" s="5" t="s">
         <v>844</v>
       </c>
-      <c r="C520" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="521" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A521" s="1" t="s">
-        <v>819</v>
-      </c>
-      <c r="B521" s="1" t="s">
+      <c r="B519" s="5" t="s">
         <v>845</v>
       </c>
-      <c r="C521" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="522" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C519" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="520" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A520" s="5" t="s">
+        <v>846</v>
+      </c>
+      <c r="B520" s="5" t="s">
+        <v>847</v>
+      </c>
+      <c r="C520" s="5" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="521" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A521" s="5" t="s">
+        <v>848</v>
+      </c>
+      <c r="B521" s="5" t="s">
+        <v>849</v>
+      </c>
+      <c r="C521" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="522" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A522" s="5" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="B522" s="5" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="C522" s="5" t="s">
-        <v>70</v>
+        <v>2</v>
       </c>
     </row>
     <row r="523" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A523" s="5" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="B523" s="5" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="C523" s="5" t="s">
-        <v>169</v>
+        <v>69</v>
       </c>
     </row>
     <row r="524" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A524" s="5" t="s">
-        <v>850</v>
+        <v>546</v>
       </c>
       <c r="B524" s="5" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="C524" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="525" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A525" s="5" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="B525" s="5" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="C525" s="5" t="s">
-        <v>2</v>
+        <v>168</v>
       </c>
     </row>
     <row r="526" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A526" s="5" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="B526" s="5" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="C526" s="5" t="s">
-        <v>70</v>
+        <v>168</v>
       </c>
     </row>
     <row r="527" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A527" s="5" t="s">
-        <v>548</v>
+        <v>859</v>
       </c>
       <c r="B527" s="5" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="C527" s="5" t="s">
-        <v>70</v>
+        <v>168</v>
       </c>
     </row>
     <row r="528" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A528" s="5" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="B528" s="5" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="C528" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="529" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A529" s="5" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="B529" s="5" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="C529" s="5" t="s">
-        <v>169</v>
+        <v>2</v>
       </c>
     </row>
     <row r="530" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A530" s="5" t="s">
-        <v>861</v>
+        <v>848</v>
       </c>
       <c r="B530" s="5" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="C530" s="5" t="s">
-        <v>169</v>
+        <v>69</v>
       </c>
     </row>
     <row r="531" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A531" s="5" t="s">
-        <v>863</v>
+        <v>848</v>
       </c>
       <c r="B531" s="5" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="C531" s="5" t="s">
-        <v>169</v>
+        <v>69</v>
       </c>
     </row>
     <row r="532" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A532" s="5" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="B532" s="5" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="C532" s="5" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="533" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A533" s="5" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="B533" s="5" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="C533" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="534" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A534" s="5" t="s">
-        <v>850</v>
+        <v>872</v>
       </c>
       <c r="B534" s="5" t="s">
-        <v>868</v>
+        <v>873</v>
       </c>
       <c r="C534" s="5" t="s">
-        <v>70</v>
+        <v>2</v>
       </c>
     </row>
     <row r="535" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A535" s="5" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="B535" s="5" t="s">
-        <v>870</v>
+        <v>875</v>
       </c>
       <c r="C535" s="5" t="s">
-        <v>70</v>
+        <v>168</v>
       </c>
     </row>
     <row r="536" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A536" s="5" t="s">
-        <v>871</v>
+        <v>876</v>
       </c>
       <c r="B536" s="5" t="s">
-        <v>872</v>
-      </c>
-      <c r="C536" s="5" t="s">
-        <v>70</v>
+        <v>877</v>
+      </c>
+      <c r="C536" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="537" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A537" s="5" t="s">
-        <v>850</v>
+        <v>878</v>
       </c>
       <c r="B537" s="5" t="s">
-        <v>873</v>
+        <v>879</v>
       </c>
       <c r="C537" s="5" t="s">
-        <v>70</v>
+        <v>168</v>
       </c>
     </row>
     <row r="538" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A538" s="5" t="s">
-        <v>874</v>
+        <v>817</v>
       </c>
       <c r="B538" s="5" t="s">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="C538" s="5" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="539" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A539" s="5" t="s">
-        <v>876</v>
+        <v>867</v>
       </c>
       <c r="B539" s="5" t="s">
-        <v>877</v>
+        <v>868</v>
       </c>
       <c r="C539" s="5" t="s">
-        <v>169</v>
+        <v>69</v>
       </c>
     </row>
     <row r="540" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A540" s="5" t="s">
-        <v>878</v>
+        <v>872</v>
       </c>
       <c r="B540" s="5" t="s">
-        <v>879</v>
-      </c>
-      <c r="C540" s="1" t="s">
-        <v>108</v>
+        <v>881</v>
+      </c>
+      <c r="C540" s="5" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="541" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A541" s="5" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="B541" s="5" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="C541" s="5" t="s">
-        <v>169</v>
+        <v>69</v>
       </c>
     </row>
     <row r="542" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A542" s="5" t="s">
-        <v>819</v>
+        <v>884</v>
       </c>
       <c r="B542" s="5" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="C542" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="543" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A543" s="5" t="s">
-        <v>869</v>
+        <v>886</v>
       </c>
       <c r="B543" s="5" t="s">
-        <v>870</v>
+        <v>887</v>
       </c>
       <c r="C543" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="544" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A544" s="5" t="s">
-        <v>874</v>
+      <c r="A544" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="B544" s="5" t="s">
-        <v>883</v>
+        <v>888</v>
       </c>
       <c r="C544" s="5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="545" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A545" s="5" t="s">
-        <v>885</v>
-      </c>
-      <c r="B545" s="5" t="s">
-        <v>884</v>
-      </c>
-      <c r="C545" s="5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="546" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A546" s="5" t="s">
-        <v>886</v>
-      </c>
-      <c r="B546" s="5" t="s">
-        <v>887</v>
-      </c>
-      <c r="C546" s="5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="547" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A547" s="5" t="s">
-        <v>888</v>
-      </c>
-      <c r="B547" s="5" t="s">
-        <v>889</v>
-      </c>
-      <c r="C547" s="5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="548" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A548" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="B548" s="5" t="s">
-        <v>890</v>
-      </c>
-      <c r="C548" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="556" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B556" s="5" t="s">
-        <v>891</v>
-      </c>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="552" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B552" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C508" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:C506" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
